--- a/data/nse/delivery/daily_output/delivery_breakout_20260710.xlsx
+++ b/data/nse/delivery/daily_output/delivery_breakout_20260710.xlsx
@@ -425,13 +425,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,378 +447,1603 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>DELIV_QTY</t>
+          <t>LTP</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>AVG_30_DELIV_QTY</t>
+          <t>TOTAL_VOLUME</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DELIVERY_QTY</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DELIVERY_%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AVG_30_DELIVERY</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>DELIVERY_RATIO</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TRADED_VALUE_CR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>DELIVERY_VALUE_CR</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GODREJIND","GODREJIND")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","KALYANKJIL")</f>
         <v/>
       </c>
       <c r="B2" t="n">
-        <v>384488</v>
+        <v>476.15</v>
       </c>
       <c r="C2" t="n">
-        <v>57073.24137931035</v>
+        <v>115487371</v>
       </c>
       <c r="D2" t="n">
-        <v>6.74</v>
+        <v>19901756</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3080821</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5498.93</v>
+      </c>
+      <c r="I2" t="n">
+        <v>947.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","KALYANKJIL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIXON","DIXON")</f>
         <v/>
       </c>
       <c r="B3" t="n">
-        <v>19901756</v>
+        <v>13421</v>
       </c>
       <c r="C3" t="n">
-        <v>3080821</v>
+        <v>1689462</v>
       </c>
       <c r="D3" t="n">
-        <v>6.46</v>
+        <v>591632</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="F3" t="n">
+        <v>174064.2413793103</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2267.43</v>
+      </c>
+      <c r="I3" t="n">
+        <v>794.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NEWGEN","NEWGEN")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CDSL","CDSL")</f>
         <v/>
       </c>
       <c r="B4" t="n">
-        <v>2415435</v>
+        <v>1431.9</v>
       </c>
       <c r="C4" t="n">
-        <v>383476.5172413793</v>
+        <v>9178914</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3</v>
+        <v>3861959</v>
+      </c>
+      <c r="E4" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="F4" t="n">
+        <v>655058.1379310344</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1314.33</v>
+      </c>
+      <c r="I4" t="n">
+        <v>552.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANHLIFE","CANHLIFE")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","DRREDDY")</f>
         <v/>
       </c>
       <c r="B5" t="n">
-        <v>2184455</v>
+        <v>1244.3</v>
       </c>
       <c r="C5" t="n">
-        <v>363208.8275862069</v>
+        <v>8106606</v>
       </c>
       <c r="D5" t="n">
-        <v>6.01</v>
+        <v>4361177</v>
+      </c>
+      <c r="E5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>864465.5862068966</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1008.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>542.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CDSL","CDSL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY","DELHIVERY")</f>
         <v/>
       </c>
       <c r="B6" t="n">
-        <v>3861959</v>
+        <v>520.3</v>
       </c>
       <c r="C6" t="n">
-        <v>655058.1379310344</v>
+        <v>13914959</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9</v>
+        <v>9405977</v>
+      </c>
+      <c r="E6" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2534128.655172414</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H6" t="n">
+        <v>724</v>
+      </c>
+      <c r="I6" t="n">
+        <v>489.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZENSARTECH","ZENSARTECH")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ETHOSLTD","ETHOSLTD")</f>
         <v/>
       </c>
       <c r="B7" t="n">
-        <v>2851264</v>
+        <v>2477.5</v>
       </c>
       <c r="C7" t="n">
-        <v>549162.1379310344</v>
+        <v>797816</v>
       </c>
       <c r="D7" t="n">
-        <v>5.19</v>
+        <v>732248</v>
+      </c>
+      <c r="E7" t="n">
+        <v>91.78</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8938.724137931034</v>
+      </c>
+      <c r="G7" t="n">
+        <v>81.92</v>
+      </c>
+      <c r="H7" t="n">
+        <v>197.66</v>
+      </c>
+      <c r="I7" t="n">
+        <v>181.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","DRREDDY")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZENSARTECH","ZENSARTECH")</f>
         <v/>
       </c>
       <c r="B8" t="n">
-        <v>4361177</v>
+        <v>508.25</v>
       </c>
       <c r="C8" t="n">
-        <v>864465.5862068966</v>
+        <v>47030557</v>
       </c>
       <c r="D8" t="n">
-        <v>5.04</v>
+        <v>2851264</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>549162.1379310344</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2390.33</v>
+      </c>
+      <c r="I8" t="n">
+        <v>144.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBFC","SBFC")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:J&amp;KBANK","J&amp;KBANK")</f>
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>3137143</v>
+        <v>192.65</v>
       </c>
       <c r="C9" t="n">
-        <v>652347.4137931034</v>
+        <v>22820672</v>
       </c>
       <c r="D9" t="n">
-        <v>4.81</v>
+        <v>7449900</v>
+      </c>
+      <c r="E9" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1952621.482758621</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="H9" t="n">
+        <v>439.64</v>
+      </c>
+      <c r="I9" t="n">
+        <v>143.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABDL","ABDL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UJJIVANSFB","UJJIVANSFB")</f>
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>929614</v>
+        <v>65.27</v>
       </c>
       <c r="C10" t="n">
-        <v>196417</v>
+        <v>39570140</v>
       </c>
       <c r="D10" t="n">
-        <v>4.73</v>
+        <v>20855448</v>
+      </c>
+      <c r="E10" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6871102.103448275</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="H10" t="n">
+        <v>258.27</v>
+      </c>
+      <c r="I10" t="n">
+        <v>136.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RHIM","RHIM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INOXWIND","INOXWIND")</f>
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>1669819</v>
+        <v>82.61</v>
       </c>
       <c r="C11" t="n">
-        <v>403329.6206896552</v>
+        <v>32213482</v>
       </c>
       <c r="D11" t="n">
-        <v>4.14</v>
+        <v>16164772</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4437049.137931035</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H11" t="n">
+        <v>266.12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>133.54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATUL","ATUL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NEWGEN","NEWGEN")</f>
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>47167</v>
+        <v>517.2</v>
       </c>
       <c r="C12" t="n">
-        <v>11932.03448275862</v>
+        <v>29948995</v>
       </c>
       <c r="D12" t="n">
-        <v>3.95</v>
+        <v>2415435</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="F12" t="n">
+        <v>383476.5172413793</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1548.96</v>
+      </c>
+      <c r="I12" t="n">
+        <v>124.93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ARE&amp;M","ARE&amp;M")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MRPL","MRPL")</f>
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>859855</v>
+        <v>162.49</v>
       </c>
       <c r="C13" t="n">
-        <v>224774.9310344828</v>
+        <v>37336927</v>
       </c>
       <c r="D13" t="n">
-        <v>3.83</v>
+        <v>6820376</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1804772.379310345</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="H13" t="n">
+        <v>606.6900000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>110.82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:J&amp;KBANK","J&amp;KBANK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GREAVESCOT","GREAVESCOT")</f>
         <v/>
       </c>
       <c r="B14" t="n">
-        <v>7449900</v>
+        <v>263.6</v>
       </c>
       <c r="C14" t="n">
-        <v>1952621.482758621</v>
+        <v>20117335</v>
       </c>
       <c r="D14" t="n">
-        <v>3.82</v>
+        <v>3405606</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="F14" t="n">
+        <v>978498.0344827586</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>530.29</v>
+      </c>
+      <c r="I14" t="n">
+        <v>89.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MRPL","MRPL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IONEXCHANG","IONEXCHANG")</f>
         <v/>
       </c>
       <c r="B15" t="n">
-        <v>6820376</v>
+        <v>468.3</v>
       </c>
       <c r="C15" t="n">
-        <v>1804772.379310345</v>
+        <v>12898024</v>
       </c>
       <c r="D15" t="n">
-        <v>3.78</v>
+        <v>1649686</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="F15" t="n">
+        <v>275632.9310344828</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="H15" t="n">
+        <v>604.01</v>
+      </c>
+      <c r="I15" t="n">
+        <v>77.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUEJET","BLUEJET")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ARE&amp;M","ARE&amp;M")</f>
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>1062858</v>
+        <v>890.05</v>
       </c>
       <c r="C16" t="n">
-        <v>283599.2413793103</v>
+        <v>1615861</v>
       </c>
       <c r="D16" t="n">
-        <v>3.75</v>
+        <v>859855</v>
+      </c>
+      <c r="E16" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="F16" t="n">
+        <v>224774.9310344828</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H16" t="n">
+        <v>143.82</v>
+      </c>
+      <c r="I16" t="n">
+        <v>76.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY","DELHIVERY")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RHIM","RHIM")</f>
         <v/>
       </c>
       <c r="B17" t="n">
-        <v>9405977</v>
+        <v>420.35</v>
       </c>
       <c r="C17" t="n">
-        <v>2534128.655172414</v>
+        <v>5014433</v>
       </c>
       <c r="D17" t="n">
-        <v>3.71</v>
+        <v>1669819</v>
+      </c>
+      <c r="E17" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>403329.6206896552</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>210.78</v>
+      </c>
+      <c r="I17" t="n">
+        <v>70.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INOXWIND","INOXWIND")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GOLDIAM","GOLDIAM")</f>
         <v/>
       </c>
       <c r="B18" t="n">
-        <v>16164772</v>
+        <v>378</v>
       </c>
       <c r="C18" t="n">
-        <v>4437049.137931035</v>
+        <v>9982384</v>
       </c>
       <c r="D18" t="n">
-        <v>3.64</v>
+        <v>1791399</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="F18" t="n">
+        <v>393139.3448275862</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H18" t="n">
+        <v>377.33</v>
+      </c>
+      <c r="I18" t="n">
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UTIAMC","UTIAMC")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUEJET","BLUEJET")</f>
         <v/>
       </c>
       <c r="B19" t="n">
-        <v>346882</v>
+        <v>624.05</v>
       </c>
       <c r="C19" t="n">
-        <v>95934.55172413793</v>
+        <v>4844866</v>
       </c>
       <c r="D19" t="n">
-        <v>3.62</v>
+        <v>1062858</v>
+      </c>
+      <c r="E19" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="F19" t="n">
+        <v>283599.2413793103</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H19" t="n">
+        <v>302.34</v>
+      </c>
+      <c r="I19" t="n">
+        <v>66.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIXON","DIXON")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EIEL","EIEL")</f>
         <v/>
       </c>
       <c r="B20" t="n">
-        <v>591632</v>
+        <v>244.49</v>
       </c>
       <c r="C20" t="n">
-        <v>174064.2413793103</v>
+        <v>9010315</v>
       </c>
       <c r="D20" t="n">
-        <v>3.4</v>
+        <v>2710990</v>
+      </c>
+      <c r="E20" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="F20" t="n">
+        <v>801091.6896551724</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="H20" t="n">
+        <v>220.29</v>
+      </c>
+      <c r="I20" t="n">
+        <v>66.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZFCVINDIA","ZFCVINDIA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","BRIGADE")</f>
         <v/>
       </c>
       <c r="B21" t="n">
-        <v>192668</v>
+        <v>574.6</v>
       </c>
       <c r="C21" t="n">
-        <v>58367.1724137931</v>
+        <v>2703568</v>
       </c>
       <c r="D21" t="n">
-        <v>3.3</v>
+        <v>1139441</v>
+      </c>
+      <c r="E21" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="F21" t="n">
+        <v>355711.6206896552</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>155.35</v>
+      </c>
+      <c r="I21" t="n">
+        <v>65.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TBOTEK","TBOTEK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABDL","ABDL")</f>
         <v/>
       </c>
       <c r="B22" t="n">
-        <v>390174</v>
+        <v>648.75</v>
       </c>
       <c r="C22" t="n">
-        <v>119174.0344827586</v>
+        <v>1420666</v>
       </c>
       <c r="D22" t="n">
-        <v>3.27</v>
+        <v>929614</v>
+      </c>
+      <c r="E22" t="n">
+        <v>65.44</v>
+      </c>
+      <c r="F22" t="n">
+        <v>196417</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H22" t="n">
+        <v>92.17</v>
+      </c>
+      <c r="I22" t="n">
+        <v>60.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","BRIGADE")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEG","HEG")</f>
         <v/>
       </c>
       <c r="B23" t="n">
-        <v>1139441</v>
+        <v>545.05</v>
       </c>
       <c r="C23" t="n">
-        <v>355711.6206896552</v>
+        <v>5160132</v>
       </c>
       <c r="D23" t="n">
-        <v>3.2</v>
+        <v>1091995</v>
+      </c>
+      <c r="E23" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>348056.7931034483</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>281.25</v>
+      </c>
+      <c r="I23" t="n">
+        <v>59.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEG","HEG")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TBOTEK","TBOTEK")</f>
         <v/>
       </c>
       <c r="B24" t="n">
-        <v>1091995</v>
+        <v>1504.9</v>
       </c>
       <c r="C24" t="n">
-        <v>348056.7931034483</v>
+        <v>442591</v>
       </c>
       <c r="D24" t="n">
-        <v>3.14</v>
+        <v>390174</v>
+      </c>
+      <c r="E24" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="F24" t="n">
+        <v>119174.0344827586</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H24" t="n">
+        <v>66.61</v>
+      </c>
+      <c r="I24" t="n">
+        <v>58.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GODREJIND","GODREJIND")</f>
+        <v/>
+      </c>
+      <c r="B25" t="n">
+        <v>1417.7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2661745</v>
+      </c>
+      <c r="D25" t="n">
+        <v>384488</v>
+      </c>
+      <c r="E25" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="F25" t="n">
+        <v>57073.24137931035</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="H25" t="n">
+        <v>377.36</v>
+      </c>
+      <c r="I25" t="n">
+        <v>54.51</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:STALLION","STALLION")</f>
+        <v/>
+      </c>
+      <c r="B26" t="n">
+        <v>204.88</v>
+      </c>
+      <c r="C26" t="n">
+        <v>16334635</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2619014</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="F26" t="n">
+        <v>621757.8275862068</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H26" t="n">
+        <v>334.66</v>
+      </c>
+      <c r="I26" t="n">
+        <v>53.66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HAPPSTMNDS","HAPPSTMNDS")</f>
+        <v/>
+      </c>
+      <c r="B27" t="n">
+        <v>386.3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4373075</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1218932</v>
+      </c>
+      <c r="E27" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="F27" t="n">
+        <v>341972.275862069</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H27" t="n">
+        <v>168.93</v>
+      </c>
+      <c r="I27" t="n">
+        <v>47.09</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUMICHEM","SUMICHEM")</f>
         <v/>
       </c>
-      <c r="B25" t="n">
+      <c r="B28" t="n">
+        <v>513.7</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2258450</v>
+      </c>
+      <c r="D28" t="n">
         <v>905164</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E28" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="F28" t="n">
         <v>300710.9655172414</v>
       </c>
-      <c r="D25" t="n">
+      <c r="G28" t="n">
         <v>3.01</v>
+      </c>
+      <c r="H28" t="n">
+        <v>116.02</v>
+      </c>
+      <c r="I28" t="n">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZFCVINDIA","ZFCVINDIA")</f>
+        <v/>
+      </c>
+      <c r="B29" t="n">
+        <v>2333.8</v>
+      </c>
+      <c r="C29" t="n">
+        <v>246194</v>
+      </c>
+      <c r="D29" t="n">
+        <v>192668</v>
+      </c>
+      <c r="E29" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>58367.1724137931</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="I29" t="n">
+        <v>44.96</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","MAHLIFE")</f>
+        <v/>
+      </c>
+      <c r="B30" t="n">
+        <v>378.9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1292886</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1184617</v>
+      </c>
+      <c r="E30" t="n">
+        <v>91.63</v>
+      </c>
+      <c r="F30" t="n">
+        <v>74574.41379310345</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="H30" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="I30" t="n">
+        <v>44.89</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMSLIMITED","EMSLIMITED")</f>
+        <v/>
+      </c>
+      <c r="B31" t="n">
+        <v>458.15</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2680107</v>
+      </c>
+      <c r="D31" t="n">
+        <v>899272</v>
+      </c>
+      <c r="E31" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="F31" t="n">
+        <v>244762.275862069</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H31" t="n">
+        <v>122.79</v>
+      </c>
+      <c r="I31" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOBIKWIK","MOBIKWIK")</f>
+        <v/>
+      </c>
+      <c r="B32" t="n">
+        <v>221.45</v>
+      </c>
+      <c r="C32" t="n">
+        <v>9125473</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1846860</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>350157.9655172414</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="H32" t="n">
+        <v>202.08</v>
+      </c>
+      <c r="I32" t="n">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NORTHARC","NORTHARC")</f>
+        <v/>
+      </c>
+      <c r="B33" t="n">
+        <v>325.3</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2149647</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1251298</v>
+      </c>
+      <c r="E33" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="F33" t="n">
+        <v>309377.2413793103</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="H33" t="n">
+        <v>69.93000000000001</v>
+      </c>
+      <c r="I33" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SENCO","SENCO")</f>
+        <v/>
+      </c>
+      <c r="B34" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4077698</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1103581</v>
+      </c>
+      <c r="E34" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="F34" t="n">
+        <v>320741.1034482759</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="H34" t="n">
+        <v>147.67</v>
+      </c>
+      <c r="I34" t="n">
+        <v>39.97</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTMF","MUTHOOTMF")</f>
+        <v/>
+      </c>
+      <c r="B35" t="n">
+        <v>235.26</v>
+      </c>
+      <c r="C35" t="n">
+        <v>19681749</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1613616</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>196233.275862069</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>463.03</v>
+      </c>
+      <c r="I35" t="n">
+        <v>37.96</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IFBIND","IFBIND")</f>
+        <v/>
+      </c>
+      <c r="B36" t="n">
+        <v>1380.5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>658386</v>
+      </c>
+      <c r="D36" t="n">
+        <v>259855</v>
+      </c>
+      <c r="E36" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="F36" t="n">
+        <v>37430.10344827586</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="H36" t="n">
+        <v>90.89</v>
+      </c>
+      <c r="I36" t="n">
+        <v>35.87</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAXESTATES","MAXESTATES")</f>
+        <v/>
+      </c>
+      <c r="B37" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="C37" t="n">
+        <v>877910</v>
+      </c>
+      <c r="D37" t="n">
+        <v>790461</v>
+      </c>
+      <c r="E37" t="n">
+        <v>90.04000000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>38060.1724137931</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="H37" t="n">
+        <v>39.46</v>
+      </c>
+      <c r="I37" t="n">
+        <v>35.53</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PGHL","PGHL")</f>
+        <v/>
+      </c>
+      <c r="B38" t="n">
+        <v>6839</v>
+      </c>
+      <c r="C38" t="n">
+        <v>82938</v>
+      </c>
+      <c r="D38" t="n">
+        <v>51538</v>
+      </c>
+      <c r="E38" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10882.34482758621</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H38" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="I38" t="n">
+        <v>35.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UTIAMC","UTIAMC")</f>
+        <v/>
+      </c>
+      <c r="B39" t="n">
+        <v>1004.3</v>
+      </c>
+      <c r="C39" t="n">
+        <v>663822</v>
+      </c>
+      <c r="D39" t="n">
+        <v>346882</v>
+      </c>
+      <c r="E39" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="F39" t="n">
+        <v>95934.55172413793</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H39" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I39" t="n">
+        <v>34.84</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUDARSCHEM","SUDARSCHEM")</f>
+        <v/>
+      </c>
+      <c r="B40" t="n">
+        <v>999.25</v>
+      </c>
+      <c r="C40" t="n">
+        <v>615230</v>
+      </c>
+      <c r="D40" t="n">
+        <v>343807</v>
+      </c>
+      <c r="E40" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="F40" t="n">
+        <v>102005.8275862069</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="H40" t="n">
+        <v>61.48</v>
+      </c>
+      <c r="I40" t="n">
+        <v>34.35</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SKFINDUS","SKFINDUS")</f>
+        <v/>
+      </c>
+      <c r="B41" t="n">
+        <v>2830.4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>146009</v>
+      </c>
+      <c r="D41" t="n">
+        <v>120539</v>
+      </c>
+      <c r="E41" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="F41" t="n">
+        <v>30121.06896551724</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="I41" t="n">
+        <v>34.12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANHLIFE","CANHLIFE")</f>
+        <v/>
+      </c>
+      <c r="B42" t="n">
+        <v>144.03</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2458962</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2184455</v>
+      </c>
+      <c r="E42" t="n">
+        <v>88.84</v>
+      </c>
+      <c r="F42" t="n">
+        <v>363208.8275862069</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H42" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="I42" t="n">
+        <v>31.46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AYE","AYE")</f>
+        <v/>
+      </c>
+      <c r="B43" t="n">
+        <v>168.82</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2422421</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1857984</v>
+      </c>
+      <c r="E43" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="F43" t="n">
+        <v>501822.6896551724</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I43" t="n">
+        <v>31.37</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BECTORFOOD","BECTORFOOD")</f>
+        <v/>
+      </c>
+      <c r="B44" t="n">
+        <v>169.37</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2452161</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1739659</v>
+      </c>
+      <c r="E44" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="F44" t="n">
+        <v>437834.0344827586</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H44" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="I44" t="n">
+        <v>29.46</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATUL","ATUL")</f>
+        <v/>
+      </c>
+      <c r="B45" t="n">
+        <v>6236</v>
+      </c>
+      <c r="C45" t="n">
+        <v>69678</v>
+      </c>
+      <c r="D45" t="n">
+        <v>47167</v>
+      </c>
+      <c r="E45" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="F45" t="n">
+        <v>11932.03448275862</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H45" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="I45" t="n">
+        <v>29.41</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCPSUBK","HDFCPSUBK")</f>
+        <v/>
+      </c>
+      <c r="B46" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4186849</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3433510</v>
+      </c>
+      <c r="E46" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="F46" t="n">
+        <v>398212.0689655172</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="H46" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="I46" t="n">
+        <v>29.33</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBFC","SBFC")</f>
+        <v/>
+      </c>
+      <c r="B47" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4451123</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3137143</v>
+      </c>
+      <c r="E47" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="F47" t="n">
+        <v>652347.4137931034</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="H47" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="I47" t="n">
+        <v>28.85</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA","EMUDHRA")</f>
+        <v/>
+      </c>
+      <c r="B48" t="n">
+        <v>455.75</v>
+      </c>
+      <c r="C48" t="n">
+        <v>6243996</v>
+      </c>
+      <c r="D48" t="n">
+        <v>585299</v>
+      </c>
+      <c r="E48" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="F48" t="n">
+        <v>54294.44827586207</v>
+      </c>
+      <c r="G48" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="H48" t="n">
+        <v>284.57</v>
+      </c>
+      <c r="I48" t="n">
+        <v>26.68</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICRA","ICRA")</f>
+        <v/>
+      </c>
+      <c r="B49" t="n">
+        <v>5298</v>
+      </c>
+      <c r="C49" t="n">
+        <v>64345</v>
+      </c>
+      <c r="D49" t="n">
+        <v>47118</v>
+      </c>
+      <c r="E49" t="n">
+        <v>73.23</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8746.758620689656</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="H49" t="n">
+        <v>34.09</v>
+      </c>
+      <c r="I49" t="n">
+        <v>24.96</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ELLEN","ELLEN")</f>
+        <v/>
+      </c>
+      <c r="B50" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1669388</v>
+      </c>
+      <c r="D50" t="n">
+        <v>839424</v>
+      </c>
+      <c r="E50" t="n">
+        <v>50.28</v>
+      </c>
+      <c r="F50" t="n">
+        <v>181662.5517241379</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H50" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="I50" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INA","INA")</f>
+        <v/>
+      </c>
+      <c r="B51" t="n">
+        <v>124.93</v>
+      </c>
+      <c r="C51" t="n">
+        <v>22232334</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1790719</v>
+      </c>
+      <c r="E51" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>384970.6206896552</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H51" t="n">
+        <v>277.75</v>
+      </c>
+      <c r="I51" t="n">
+        <v>22.37</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KODYTECH","KODYTECH")</f>
+        <v/>
+      </c>
+      <c r="B52" t="n">
+        <v>1216.75</v>
+      </c>
+      <c r="C52" t="n">
+        <v>221500</v>
+      </c>
+      <c r="D52" t="n">
+        <v>179200</v>
+      </c>
+      <c r="E52" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="F52" t="n">
+        <v>19962.06896551724</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="H52" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="I52" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOLARA","SOLARA")</f>
+        <v/>
+      </c>
+      <c r="B53" t="n">
+        <v>568.9</v>
+      </c>
+      <c r="C53" t="n">
+        <v>838612</v>
+      </c>
+      <c r="D53" t="n">
+        <v>363229</v>
+      </c>
+      <c r="E53" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="F53" t="n">
+        <v>101553.0344827586</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H53" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="I53" t="n">
+        <v>20.66</v>
       </c>
     </row>
   </sheetData>

--- a/data/nse/delivery/daily_output/delivery_breakout_20260710.xlsx
+++ b/data/nse/delivery/daily_output/delivery_breakout_20260710.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -433,7 +433,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -504,10 +504,10 @@
         <v>17.23</v>
       </c>
       <c r="F2" t="n">
-        <v>3080821</v>
+        <v>1920031</v>
       </c>
       <c r="G2" t="n">
-        <v>6.46</v>
+        <v>10.37</v>
       </c>
       <c r="H2" t="n">
         <v>5498.93</v>
@@ -518,1532 +518,1082 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIXON","DIXON")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CDSL","CDSL")</f>
         <v/>
       </c>
       <c r="B3" t="n">
-        <v>13421</v>
+        <v>1431.9</v>
       </c>
       <c r="C3" t="n">
-        <v>1689462</v>
+        <v>9178914</v>
       </c>
       <c r="D3" t="n">
-        <v>591632</v>
+        <v>3861959</v>
       </c>
       <c r="E3" t="n">
-        <v>35.02</v>
+        <v>42.07</v>
       </c>
       <c r="F3" t="n">
-        <v>174064.2413793103</v>
+        <v>502596</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4</v>
+        <v>7.68</v>
       </c>
       <c r="H3" t="n">
-        <v>2267.43</v>
+        <v>1314.33</v>
       </c>
       <c r="I3" t="n">
-        <v>794.03</v>
+        <v>552.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CDSL","CDSL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","DRREDDY")</f>
         <v/>
       </c>
       <c r="B4" t="n">
-        <v>1431.9</v>
+        <v>1244.3</v>
       </c>
       <c r="C4" t="n">
-        <v>9178914</v>
+        <v>8106606</v>
       </c>
       <c r="D4" t="n">
-        <v>3861959</v>
+        <v>4361177</v>
       </c>
       <c r="E4" t="n">
-        <v>42.07</v>
+        <v>53.8</v>
       </c>
       <c r="F4" t="n">
-        <v>655058.1379310344</v>
+        <v>655147</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9</v>
+        <v>6.66</v>
       </c>
       <c r="H4" t="n">
-        <v>1314.33</v>
+        <v>1008.7</v>
       </c>
       <c r="I4" t="n">
-        <v>552.99</v>
+        <v>542.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","DRREDDY")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY","DELHIVERY")</f>
         <v/>
       </c>
       <c r="B5" t="n">
-        <v>1244.3</v>
+        <v>520.3</v>
       </c>
       <c r="C5" t="n">
-        <v>8106606</v>
+        <v>13914959</v>
       </c>
       <c r="D5" t="n">
-        <v>4361177</v>
+        <v>9405977</v>
       </c>
       <c r="E5" t="n">
-        <v>53.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>864465.5862068966</v>
+        <v>1517756</v>
       </c>
       <c r="G5" t="n">
-        <v>5.04</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1008.7</v>
+        <v>724</v>
       </c>
       <c r="I5" t="n">
-        <v>542.66</v>
+        <v>489.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY","DELHIVERY")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ETHOSLTD","ETHOSLTD")</f>
         <v/>
       </c>
       <c r="B6" t="n">
-        <v>520.3</v>
+        <v>2477.5</v>
       </c>
       <c r="C6" t="n">
-        <v>13914959</v>
+        <v>797816</v>
       </c>
       <c r="D6" t="n">
-        <v>9405977</v>
+        <v>732248</v>
       </c>
       <c r="E6" t="n">
-        <v>67.59999999999999</v>
+        <v>91.78</v>
       </c>
       <c r="F6" t="n">
-        <v>2534128.655172414</v>
+        <v>6753</v>
       </c>
       <c r="G6" t="n">
-        <v>3.71</v>
+        <v>108.43</v>
       </c>
       <c r="H6" t="n">
-        <v>724</v>
+        <v>197.66</v>
       </c>
       <c r="I6" t="n">
-        <v>489.39</v>
+        <v>181.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ETHOSLTD","ETHOSLTD")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZENSARTECH","ZENSARTECH")</f>
         <v/>
       </c>
       <c r="B7" t="n">
-        <v>2477.5</v>
+        <v>508.25</v>
       </c>
       <c r="C7" t="n">
-        <v>797816</v>
+        <v>47030557</v>
       </c>
       <c r="D7" t="n">
-        <v>732248</v>
+        <v>2851264</v>
       </c>
       <c r="E7" t="n">
-        <v>91.78</v>
+        <v>6.06</v>
       </c>
       <c r="F7" t="n">
-        <v>8938.724137931034</v>
+        <v>305011</v>
       </c>
       <c r="G7" t="n">
-        <v>81.92</v>
+        <v>9.35</v>
       </c>
       <c r="H7" t="n">
-        <v>197.66</v>
+        <v>2390.33</v>
       </c>
       <c r="I7" t="n">
-        <v>181.41</v>
+        <v>144.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZENSARTECH","ZENSARTECH")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NEWGEN","NEWGEN")</f>
         <v/>
       </c>
       <c r="B8" t="n">
-        <v>508.25</v>
+        <v>517.2</v>
       </c>
       <c r="C8" t="n">
-        <v>47030557</v>
+        <v>29948995</v>
       </c>
       <c r="D8" t="n">
-        <v>2851264</v>
+        <v>2415435</v>
       </c>
       <c r="E8" t="n">
-        <v>6.06</v>
+        <v>8.07</v>
       </c>
       <c r="F8" t="n">
-        <v>549162.1379310344</v>
+        <v>212961</v>
       </c>
       <c r="G8" t="n">
-        <v>5.19</v>
+        <v>11.34</v>
       </c>
       <c r="H8" t="n">
-        <v>2390.33</v>
+        <v>1548.96</v>
       </c>
       <c r="I8" t="n">
-        <v>144.92</v>
+        <v>124.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:J&amp;KBANK","J&amp;KBANK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MRPL","MRPL")</f>
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>192.65</v>
+        <v>162.49</v>
       </c>
       <c r="C9" t="n">
-        <v>22820672</v>
+        <v>37336927</v>
       </c>
       <c r="D9" t="n">
-        <v>7449900</v>
+        <v>6820376</v>
       </c>
       <c r="E9" t="n">
-        <v>32.65</v>
+        <v>18.27</v>
       </c>
       <c r="F9" t="n">
-        <v>1952621.482758621</v>
+        <v>1324216</v>
       </c>
       <c r="G9" t="n">
-        <v>3.82</v>
+        <v>5.15</v>
       </c>
       <c r="H9" t="n">
-        <v>439.64</v>
+        <v>606.6900000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>143.52</v>
+        <v>110.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UJJIVANSFB","UJJIVANSFB")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IONEXCHANG","IONEXCHANG")</f>
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>65.27</v>
+        <v>468.3</v>
       </c>
       <c r="C10" t="n">
-        <v>39570140</v>
+        <v>12898024</v>
       </c>
       <c r="D10" t="n">
-        <v>20855448</v>
+        <v>1649686</v>
       </c>
       <c r="E10" t="n">
-        <v>52.71</v>
+        <v>12.79</v>
       </c>
       <c r="F10" t="n">
-        <v>6871102.103448275</v>
+        <v>199503</v>
       </c>
       <c r="G10" t="n">
-        <v>3.04</v>
+        <v>8.27</v>
       </c>
       <c r="H10" t="n">
-        <v>258.27</v>
+        <v>604.01</v>
       </c>
       <c r="I10" t="n">
-        <v>136.12</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INOXWIND","INOXWIND")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RHIM","RHIM")</f>
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>82.61</v>
+        <v>420.35</v>
       </c>
       <c r="C11" t="n">
-        <v>32213482</v>
+        <v>5014433</v>
       </c>
       <c r="D11" t="n">
-        <v>16164772</v>
+        <v>1669819</v>
       </c>
       <c r="E11" t="n">
-        <v>50.18</v>
+        <v>33.3</v>
       </c>
       <c r="F11" t="n">
-        <v>4437049.137931035</v>
+        <v>143864</v>
       </c>
       <c r="G11" t="n">
-        <v>3.64</v>
+        <v>11.61</v>
       </c>
       <c r="H11" t="n">
-        <v>266.12</v>
+        <v>210.78</v>
       </c>
       <c r="I11" t="n">
-        <v>133.54</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NEWGEN","NEWGEN")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GOLDIAM","GOLDIAM")</f>
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>517.2</v>
+        <v>378</v>
       </c>
       <c r="C12" t="n">
-        <v>29948995</v>
+        <v>9982384</v>
       </c>
       <c r="D12" t="n">
-        <v>2415435</v>
+        <v>1791399</v>
       </c>
       <c r="E12" t="n">
-        <v>8.07</v>
+        <v>17.95</v>
       </c>
       <c r="F12" t="n">
-        <v>383476.5172413793</v>
+        <v>337267</v>
       </c>
       <c r="G12" t="n">
-        <v>6.3</v>
+        <v>5.31</v>
       </c>
       <c r="H12" t="n">
-        <v>1548.96</v>
+        <v>377.33</v>
       </c>
       <c r="I12" t="n">
-        <v>124.93</v>
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MRPL","MRPL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABDL","ABDL")</f>
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>162.49</v>
+        <v>648.75</v>
       </c>
       <c r="C13" t="n">
-        <v>37336927</v>
+        <v>1420666</v>
       </c>
       <c r="D13" t="n">
-        <v>6820376</v>
+        <v>929614</v>
       </c>
       <c r="E13" t="n">
-        <v>18.27</v>
+        <v>65.44</v>
       </c>
       <c r="F13" t="n">
-        <v>1804772.379310345</v>
+        <v>148904</v>
       </c>
       <c r="G13" t="n">
-        <v>3.78</v>
+        <v>6.24</v>
       </c>
       <c r="H13" t="n">
-        <v>606.6900000000001</v>
+        <v>92.17</v>
       </c>
       <c r="I13" t="n">
-        <v>110.82</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GREAVESCOT","GREAVESCOT")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TBOTEK","TBOTEK")</f>
         <v/>
       </c>
       <c r="B14" t="n">
-        <v>263.6</v>
+        <v>1504.9</v>
       </c>
       <c r="C14" t="n">
-        <v>20117335</v>
+        <v>442591</v>
       </c>
       <c r="D14" t="n">
-        <v>3405606</v>
+        <v>390174</v>
       </c>
       <c r="E14" t="n">
-        <v>16.93</v>
+        <v>88.16</v>
       </c>
       <c r="F14" t="n">
-        <v>978498.0344827586</v>
+        <v>53117</v>
       </c>
       <c r="G14" t="n">
-        <v>3.48</v>
+        <v>7.35</v>
       </c>
       <c r="H14" t="n">
-        <v>530.29</v>
+        <v>66.61</v>
       </c>
       <c r="I14" t="n">
-        <v>89.77</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IONEXCHANG","IONEXCHANG")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GODREJIND","GODREJIND")</f>
         <v/>
       </c>
       <c r="B15" t="n">
-        <v>468.3</v>
+        <v>1417.7</v>
       </c>
       <c r="C15" t="n">
-        <v>12898024</v>
+        <v>2661745</v>
       </c>
       <c r="D15" t="n">
-        <v>1649686</v>
+        <v>384488</v>
       </c>
       <c r="E15" t="n">
-        <v>12.79</v>
+        <v>14.44</v>
       </c>
       <c r="F15" t="n">
-        <v>275632.9310344828</v>
+        <v>54457</v>
       </c>
       <c r="G15" t="n">
-        <v>5.99</v>
+        <v>7.06</v>
       </c>
       <c r="H15" t="n">
-        <v>604.01</v>
+        <v>377.36</v>
       </c>
       <c r="I15" t="n">
-        <v>77.25</v>
+        <v>54.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ARE&amp;M","ARE&amp;M")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:STALLION","STALLION")</f>
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>890.05</v>
+        <v>204.88</v>
       </c>
       <c r="C16" t="n">
-        <v>1615861</v>
+        <v>16334635</v>
       </c>
       <c r="D16" t="n">
-        <v>859855</v>
+        <v>2619014</v>
       </c>
       <c r="E16" t="n">
-        <v>53.21</v>
+        <v>16.03</v>
       </c>
       <c r="F16" t="n">
-        <v>224774.9310344828</v>
+        <v>491381</v>
       </c>
       <c r="G16" t="n">
-        <v>3.83</v>
+        <v>5.33</v>
       </c>
       <c r="H16" t="n">
-        <v>143.82</v>
+        <v>334.66</v>
       </c>
       <c r="I16" t="n">
-        <v>76.53</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RHIM","RHIM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HAPPSTMNDS","HAPPSTMNDS")</f>
         <v/>
       </c>
       <c r="B17" t="n">
-        <v>420.35</v>
+        <v>386.3</v>
       </c>
       <c r="C17" t="n">
-        <v>5014433</v>
+        <v>4373075</v>
       </c>
       <c r="D17" t="n">
-        <v>1669819</v>
+        <v>1218932</v>
       </c>
       <c r="E17" t="n">
-        <v>33.3</v>
+        <v>27.87</v>
       </c>
       <c r="F17" t="n">
-        <v>403329.6206896552</v>
+        <v>224421</v>
       </c>
       <c r="G17" t="n">
-        <v>4.14</v>
+        <v>5.43</v>
       </c>
       <c r="H17" t="n">
-        <v>210.78</v>
+        <v>168.93</v>
       </c>
       <c r="I17" t="n">
-        <v>70.19</v>
+        <v>47.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GOLDIAM","GOLDIAM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUMICHEM","SUMICHEM")</f>
         <v/>
       </c>
       <c r="B18" t="n">
-        <v>378</v>
+        <v>513.7</v>
       </c>
       <c r="C18" t="n">
-        <v>9982384</v>
+        <v>2258450</v>
       </c>
       <c r="D18" t="n">
-        <v>1791399</v>
+        <v>905164</v>
       </c>
       <c r="E18" t="n">
-        <v>17.95</v>
+        <v>40.08</v>
       </c>
       <c r="F18" t="n">
-        <v>393139.3448275862</v>
+        <v>124584</v>
       </c>
       <c r="G18" t="n">
-        <v>4.56</v>
+        <v>7.27</v>
       </c>
       <c r="H18" t="n">
-        <v>377.33</v>
+        <v>116.02</v>
       </c>
       <c r="I18" t="n">
-        <v>67.70999999999999</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUEJET","BLUEJET")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZFCVINDIA","ZFCVINDIA")</f>
         <v/>
       </c>
       <c r="B19" t="n">
-        <v>624.05</v>
+        <v>2333.8</v>
       </c>
       <c r="C19" t="n">
-        <v>4844866</v>
+        <v>246194</v>
       </c>
       <c r="D19" t="n">
-        <v>1062858</v>
+        <v>192668</v>
       </c>
       <c r="E19" t="n">
-        <v>21.94</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>283599.2413793103</v>
+        <v>20838</v>
       </c>
       <c r="G19" t="n">
-        <v>3.75</v>
+        <v>9.25</v>
       </c>
       <c r="H19" t="n">
-        <v>302.34</v>
+        <v>57.46</v>
       </c>
       <c r="I19" t="n">
-        <v>66.33</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EIEL","EIEL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","MAHLIFE")</f>
         <v/>
       </c>
       <c r="B20" t="n">
-        <v>244.49</v>
+        <v>378.9</v>
       </c>
       <c r="C20" t="n">
-        <v>9010315</v>
+        <v>1292886</v>
       </c>
       <c r="D20" t="n">
-        <v>2710990</v>
+        <v>1184617</v>
       </c>
       <c r="E20" t="n">
-        <v>30.09</v>
+        <v>91.63</v>
       </c>
       <c r="F20" t="n">
-        <v>801091.6896551724</v>
+        <v>61803</v>
       </c>
       <c r="G20" t="n">
-        <v>3.38</v>
+        <v>19.17</v>
       </c>
       <c r="H20" t="n">
-        <v>220.29</v>
+        <v>48.99</v>
       </c>
       <c r="I20" t="n">
-        <v>66.28</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","BRIGADE")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMSLIMITED","EMSLIMITED")</f>
         <v/>
       </c>
       <c r="B21" t="n">
-        <v>574.6</v>
+        <v>458.15</v>
       </c>
       <c r="C21" t="n">
-        <v>2703568</v>
+        <v>2680107</v>
       </c>
       <c r="D21" t="n">
-        <v>1139441</v>
+        <v>899272</v>
       </c>
       <c r="E21" t="n">
-        <v>42.15</v>
+        <v>33.55</v>
       </c>
       <c r="F21" t="n">
-        <v>355711.6206896552</v>
+        <v>170521</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2</v>
+        <v>5.27</v>
       </c>
       <c r="H21" t="n">
-        <v>155.35</v>
+        <v>122.79</v>
       </c>
       <c r="I21" t="n">
-        <v>65.47</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABDL","ABDL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOBIKWIK","MOBIKWIK")</f>
         <v/>
       </c>
       <c r="B22" t="n">
-        <v>648.75</v>
+        <v>221.45</v>
       </c>
       <c r="C22" t="n">
-        <v>1420666</v>
+        <v>9125473</v>
       </c>
       <c r="D22" t="n">
-        <v>929614</v>
+        <v>1846860</v>
       </c>
       <c r="E22" t="n">
-        <v>65.44</v>
+        <v>20.24</v>
       </c>
       <c r="F22" t="n">
-        <v>196417</v>
+        <v>243565</v>
       </c>
       <c r="G22" t="n">
-        <v>4.73</v>
+        <v>7.58</v>
       </c>
       <c r="H22" t="n">
-        <v>92.17</v>
+        <v>202.08</v>
       </c>
       <c r="I22" t="n">
-        <v>60.31</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEG","HEG")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SENCO","SENCO")</f>
         <v/>
       </c>
       <c r="B23" t="n">
-        <v>545.05</v>
+        <v>362.15</v>
       </c>
       <c r="C23" t="n">
-        <v>5160132</v>
+        <v>4077698</v>
       </c>
       <c r="D23" t="n">
-        <v>1091995</v>
+        <v>1103581</v>
       </c>
       <c r="E23" t="n">
-        <v>21.16</v>
+        <v>27.06</v>
       </c>
       <c r="F23" t="n">
-        <v>348056.7931034483</v>
+        <v>193516</v>
       </c>
       <c r="G23" t="n">
-        <v>3.14</v>
+        <v>5.7</v>
       </c>
       <c r="H23" t="n">
-        <v>281.25</v>
+        <v>147.67</v>
       </c>
       <c r="I23" t="n">
-        <v>59.52</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TBOTEK","TBOTEK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTMF","MUTHOOTMF")</f>
         <v/>
       </c>
       <c r="B24" t="n">
-        <v>1504.9</v>
+        <v>235.26</v>
       </c>
       <c r="C24" t="n">
-        <v>442591</v>
+        <v>19681749</v>
       </c>
       <c r="D24" t="n">
-        <v>390174</v>
+        <v>1613616</v>
       </c>
       <c r="E24" t="n">
-        <v>88.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>119174.0344827586</v>
+        <v>144018</v>
       </c>
       <c r="G24" t="n">
-        <v>3.27</v>
+        <v>11.2</v>
       </c>
       <c r="H24" t="n">
-        <v>66.61</v>
+        <v>463.03</v>
       </c>
       <c r="I24" t="n">
-        <v>58.72</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GODREJIND","GODREJIND")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IFBIND","IFBIND")</f>
         <v/>
       </c>
       <c r="B25" t="n">
-        <v>1417.7</v>
+        <v>1380.5</v>
       </c>
       <c r="C25" t="n">
-        <v>2661745</v>
+        <v>658386</v>
       </c>
       <c r="D25" t="n">
-        <v>384488</v>
+        <v>259855</v>
       </c>
       <c r="E25" t="n">
-        <v>14.44</v>
+        <v>39.47</v>
       </c>
       <c r="F25" t="n">
-        <v>57073.24137931035</v>
+        <v>27246</v>
       </c>
       <c r="G25" t="n">
-        <v>6.74</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>377.36</v>
+        <v>90.89</v>
       </c>
       <c r="I25" t="n">
-        <v>54.51</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:STALLION","STALLION")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAXESTATES","MAXESTATES")</f>
         <v/>
       </c>
       <c r="B26" t="n">
-        <v>204.88</v>
+        <v>449.5</v>
       </c>
       <c r="C26" t="n">
-        <v>16334635</v>
+        <v>877910</v>
       </c>
       <c r="D26" t="n">
-        <v>2619014</v>
+        <v>790461</v>
       </c>
       <c r="E26" t="n">
-        <v>16.03</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>621757.8275862068</v>
+        <v>24796</v>
       </c>
       <c r="G26" t="n">
-        <v>4.21</v>
+        <v>31.88</v>
       </c>
       <c r="H26" t="n">
-        <v>334.66</v>
+        <v>39.46</v>
       </c>
       <c r="I26" t="n">
-        <v>53.66</v>
+        <v>35.53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HAPPSTMNDS","HAPPSTMNDS")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PGHL","PGHL")</f>
         <v/>
       </c>
       <c r="B27" t="n">
-        <v>386.3</v>
+        <v>6839</v>
       </c>
       <c r="C27" t="n">
-        <v>4373075</v>
+        <v>82938</v>
       </c>
       <c r="D27" t="n">
-        <v>1218932</v>
+        <v>51538</v>
       </c>
       <c r="E27" t="n">
-        <v>27.87</v>
+        <v>62.14</v>
       </c>
       <c r="F27" t="n">
-        <v>341972.275862069</v>
+        <v>7808</v>
       </c>
       <c r="G27" t="n">
-        <v>3.56</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
-        <v>168.93</v>
+        <v>56.72</v>
       </c>
       <c r="I27" t="n">
-        <v>47.09</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUMICHEM","SUMICHEM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SKFINDUS","SKFINDUS")</f>
         <v/>
       </c>
       <c r="B28" t="n">
-        <v>513.7</v>
+        <v>2830.4</v>
       </c>
       <c r="C28" t="n">
-        <v>2258450</v>
+        <v>146009</v>
       </c>
       <c r="D28" t="n">
-        <v>905164</v>
+        <v>120539</v>
       </c>
       <c r="E28" t="n">
-        <v>40.08</v>
+        <v>82.56</v>
       </c>
       <c r="F28" t="n">
-        <v>300710.9655172414</v>
+        <v>17864</v>
       </c>
       <c r="G28" t="n">
-        <v>3.01</v>
+        <v>6.75</v>
       </c>
       <c r="H28" t="n">
-        <v>116.02</v>
+        <v>41.33</v>
       </c>
       <c r="I28" t="n">
-        <v>46.5</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZFCVINDIA","ZFCVINDIA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANHLIFE","CANHLIFE")</f>
         <v/>
       </c>
       <c r="B29" t="n">
-        <v>2333.8</v>
+        <v>144.03</v>
       </c>
       <c r="C29" t="n">
-        <v>246194</v>
+        <v>2458962</v>
       </c>
       <c r="D29" t="n">
-        <v>192668</v>
+        <v>2184455</v>
       </c>
       <c r="E29" t="n">
-        <v>78.26000000000001</v>
+        <v>88.84</v>
       </c>
       <c r="F29" t="n">
-        <v>58367.1724137931</v>
+        <v>300124</v>
       </c>
       <c r="G29" t="n">
-        <v>3.3</v>
+        <v>7.28</v>
       </c>
       <c r="H29" t="n">
-        <v>57.46</v>
+        <v>35.42</v>
       </c>
       <c r="I29" t="n">
-        <v>44.96</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","MAHLIFE")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BECTORFOOD","BECTORFOOD")</f>
         <v/>
       </c>
       <c r="B30" t="n">
-        <v>378.9</v>
+        <v>169.37</v>
       </c>
       <c r="C30" t="n">
-        <v>1292886</v>
+        <v>2452161</v>
       </c>
       <c r="D30" t="n">
-        <v>1184617</v>
+        <v>1739659</v>
       </c>
       <c r="E30" t="n">
-        <v>91.63</v>
+        <v>70.94</v>
       </c>
       <c r="F30" t="n">
-        <v>74574.41379310345</v>
+        <v>310585</v>
       </c>
       <c r="G30" t="n">
-        <v>15.89</v>
+        <v>5.6</v>
       </c>
       <c r="H30" t="n">
-        <v>48.99</v>
+        <v>41.53</v>
       </c>
       <c r="I30" t="n">
-        <v>44.89</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMSLIMITED","EMSLIMITED")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCPSUBK","HDFCPSUBK")</f>
         <v/>
       </c>
       <c r="B31" t="n">
-        <v>458.15</v>
+        <v>85.41</v>
       </c>
       <c r="C31" t="n">
-        <v>2680107</v>
+        <v>4186849</v>
       </c>
       <c r="D31" t="n">
-        <v>899272</v>
+        <v>3433510</v>
       </c>
       <c r="E31" t="n">
-        <v>33.55</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>244762.275862069</v>
+        <v>45800</v>
       </c>
       <c r="G31" t="n">
-        <v>3.67</v>
+        <v>74.97</v>
       </c>
       <c r="H31" t="n">
-        <v>122.79</v>
+        <v>35.76</v>
       </c>
       <c r="I31" t="n">
-        <v>41.2</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOBIKWIK","MOBIKWIK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBFC","SBFC")</f>
         <v/>
       </c>
       <c r="B32" t="n">
-        <v>221.45</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>9125473</v>
+        <v>4451123</v>
       </c>
       <c r="D32" t="n">
-        <v>1846860</v>
+        <v>3137143</v>
       </c>
       <c r="E32" t="n">
-        <v>20.24</v>
+        <v>70.48</v>
       </c>
       <c r="F32" t="n">
-        <v>350157.9655172414</v>
+        <v>455078</v>
       </c>
       <c r="G32" t="n">
-        <v>5.27</v>
+        <v>6.89</v>
       </c>
       <c r="H32" t="n">
-        <v>202.08</v>
+        <v>40.93</v>
       </c>
       <c r="I32" t="n">
-        <v>40.9</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NORTHARC","NORTHARC")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA","EMUDHRA")</f>
         <v/>
       </c>
       <c r="B33" t="n">
-        <v>325.3</v>
+        <v>455.75</v>
       </c>
       <c r="C33" t="n">
-        <v>2149647</v>
+        <v>6243996</v>
       </c>
       <c r="D33" t="n">
-        <v>1251298</v>
+        <v>585299</v>
       </c>
       <c r="E33" t="n">
-        <v>58.21</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>309377.2413793103</v>
+        <v>31913</v>
       </c>
       <c r="G33" t="n">
-        <v>4.04</v>
+        <v>18.34</v>
       </c>
       <c r="H33" t="n">
-        <v>69.93000000000001</v>
+        <v>284.57</v>
       </c>
       <c r="I33" t="n">
-        <v>40.7</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SENCO","SENCO")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICRA","ICRA")</f>
         <v/>
       </c>
       <c r="B34" t="n">
-        <v>362.15</v>
+        <v>5298</v>
       </c>
       <c r="C34" t="n">
-        <v>4077698</v>
+        <v>64345</v>
       </c>
       <c r="D34" t="n">
-        <v>1103581</v>
+        <v>47118</v>
       </c>
       <c r="E34" t="n">
-        <v>27.06</v>
+        <v>73.23</v>
       </c>
       <c r="F34" t="n">
-        <v>320741.1034482759</v>
+        <v>5249</v>
       </c>
       <c r="G34" t="n">
-        <v>3.44</v>
+        <v>8.98</v>
       </c>
       <c r="H34" t="n">
-        <v>147.67</v>
+        <v>34.09</v>
       </c>
       <c r="I34" t="n">
-        <v>39.97</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTMF","MUTHOOTMF")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ELLEN","ELLEN")</f>
         <v/>
       </c>
       <c r="B35" t="n">
-        <v>235.26</v>
+        <v>294.25</v>
       </c>
       <c r="C35" t="n">
-        <v>19681749</v>
+        <v>1669388</v>
       </c>
       <c r="D35" t="n">
-        <v>1613616</v>
+        <v>839424</v>
       </c>
       <c r="E35" t="n">
-        <v>8.199999999999999</v>
+        <v>50.28</v>
       </c>
       <c r="F35" t="n">
-        <v>196233.275862069</v>
+        <v>122144</v>
       </c>
       <c r="G35" t="n">
-        <v>8.220000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="H35" t="n">
-        <v>463.03</v>
+        <v>49.12</v>
       </c>
       <c r="I35" t="n">
-        <v>37.96</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IFBIND","IFBIND")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INA","INA")</f>
         <v/>
       </c>
       <c r="B36" t="n">
-        <v>1380.5</v>
+        <v>124.93</v>
       </c>
       <c r="C36" t="n">
-        <v>658386</v>
+        <v>22232334</v>
       </c>
       <c r="D36" t="n">
-        <v>259855</v>
+        <v>1790719</v>
       </c>
       <c r="E36" t="n">
-        <v>39.47</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>37430.10344827586</v>
+        <v>264131</v>
       </c>
       <c r="G36" t="n">
-        <v>6.94</v>
+        <v>6.78</v>
       </c>
       <c r="H36" t="n">
-        <v>90.89</v>
+        <v>277.75</v>
       </c>
       <c r="I36" t="n">
-        <v>35.87</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAXESTATES","MAXESTATES")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KODYTECH","KODYTECH")</f>
         <v/>
       </c>
       <c r="B37" t="n">
-        <v>449.5</v>
+        <v>1216.75</v>
       </c>
       <c r="C37" t="n">
-        <v>877910</v>
+        <v>221500</v>
       </c>
       <c r="D37" t="n">
-        <v>790461</v>
+        <v>179200</v>
       </c>
       <c r="E37" t="n">
-        <v>90.04000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>38060.1724137931</v>
+        <v>9500</v>
       </c>
       <c r="G37" t="n">
-        <v>20.77</v>
+        <v>18.86</v>
       </c>
       <c r="H37" t="n">
-        <v>39.46</v>
+        <v>26.95</v>
       </c>
       <c r="I37" t="n">
-        <v>35.53</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PGHL","PGHL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ITDC","ITDC")</f>
         <v/>
       </c>
       <c r="B38" t="n">
-        <v>6839</v>
+        <v>716.8</v>
       </c>
       <c r="C38" t="n">
-        <v>82938</v>
+        <v>3469655</v>
       </c>
       <c r="D38" t="n">
-        <v>51538</v>
+        <v>293035</v>
       </c>
       <c r="E38" t="n">
-        <v>62.14</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>10882.34482758621</v>
+        <v>50591</v>
       </c>
       <c r="G38" t="n">
-        <v>4.74</v>
+        <v>5.79</v>
       </c>
       <c r="H38" t="n">
-        <v>56.72</v>
+        <v>248.7</v>
       </c>
       <c r="I38" t="n">
-        <v>35.25</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UTIAMC","UTIAMC")</f>
-        <v/>
-      </c>
-      <c r="B39" t="n">
-        <v>1004.3</v>
-      </c>
-      <c r="C39" t="n">
-        <v>663822</v>
-      </c>
-      <c r="D39" t="n">
-        <v>346882</v>
-      </c>
-      <c r="E39" t="n">
-        <v>52.26</v>
-      </c>
-      <c r="F39" t="n">
-        <v>95934.55172413793</v>
-      </c>
-      <c r="G39" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="H39" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="I39" t="n">
-        <v>34.84</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUDARSCHEM","SUDARSCHEM")</f>
-        <v/>
-      </c>
-      <c r="B40" t="n">
-        <v>999.25</v>
-      </c>
-      <c r="C40" t="n">
-        <v>615230</v>
-      </c>
-      <c r="D40" t="n">
-        <v>343807</v>
-      </c>
-      <c r="E40" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="F40" t="n">
-        <v>102005.8275862069</v>
-      </c>
-      <c r="G40" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="H40" t="n">
-        <v>61.48</v>
-      </c>
-      <c r="I40" t="n">
-        <v>34.35</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SKFINDUS","SKFINDUS")</f>
-        <v/>
-      </c>
-      <c r="B41" t="n">
-        <v>2830.4</v>
-      </c>
-      <c r="C41" t="n">
-        <v>146009</v>
-      </c>
-      <c r="D41" t="n">
-        <v>120539</v>
-      </c>
-      <c r="E41" t="n">
-        <v>82.56</v>
-      </c>
-      <c r="F41" t="n">
-        <v>30121.06896551724</v>
-      </c>
-      <c r="G41" t="n">
-        <v>4</v>
-      </c>
-      <c r="H41" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="I41" t="n">
-        <v>34.12</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANHLIFE","CANHLIFE")</f>
-        <v/>
-      </c>
-      <c r="B42" t="n">
-        <v>144.03</v>
-      </c>
-      <c r="C42" t="n">
-        <v>2458962</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2184455</v>
-      </c>
-      <c r="E42" t="n">
-        <v>88.84</v>
-      </c>
-      <c r="F42" t="n">
-        <v>363208.8275862069</v>
-      </c>
-      <c r="G42" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="H42" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="I42" t="n">
-        <v>31.46</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AYE","AYE")</f>
-        <v/>
-      </c>
-      <c r="B43" t="n">
-        <v>168.82</v>
-      </c>
-      <c r="C43" t="n">
-        <v>2422421</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1857984</v>
-      </c>
-      <c r="E43" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="F43" t="n">
-        <v>501822.6896551724</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H43" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="I43" t="n">
-        <v>31.37</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BECTORFOOD","BECTORFOOD")</f>
-        <v/>
-      </c>
-      <c r="B44" t="n">
-        <v>169.37</v>
-      </c>
-      <c r="C44" t="n">
-        <v>2452161</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1739659</v>
-      </c>
-      <c r="E44" t="n">
-        <v>70.94</v>
-      </c>
-      <c r="F44" t="n">
-        <v>437834.0344827586</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="H44" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="I44" t="n">
-        <v>29.46</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATUL","ATUL")</f>
-        <v/>
-      </c>
-      <c r="B45" t="n">
-        <v>6236</v>
-      </c>
-      <c r="C45" t="n">
-        <v>69678</v>
-      </c>
-      <c r="D45" t="n">
-        <v>47167</v>
-      </c>
-      <c r="E45" t="n">
-        <v>67.69</v>
-      </c>
-      <c r="F45" t="n">
-        <v>11932.03448275862</v>
-      </c>
-      <c r="G45" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H45" t="n">
-        <v>43.45</v>
-      </c>
-      <c r="I45" t="n">
-        <v>29.41</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCPSUBK","HDFCPSUBK")</f>
-        <v/>
-      </c>
-      <c r="B46" t="n">
-        <v>85.41</v>
-      </c>
-      <c r="C46" t="n">
-        <v>4186849</v>
-      </c>
-      <c r="D46" t="n">
-        <v>3433510</v>
-      </c>
-      <c r="E46" t="n">
-        <v>82.01000000000001</v>
-      </c>
-      <c r="F46" t="n">
-        <v>398212.0689655172</v>
-      </c>
-      <c r="G46" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="H46" t="n">
-        <v>35.76</v>
-      </c>
-      <c r="I46" t="n">
-        <v>29.33</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBFC","SBFC")</f>
-        <v/>
-      </c>
-      <c r="B47" t="n">
-        <v>91.95999999999999</v>
-      </c>
-      <c r="C47" t="n">
-        <v>4451123</v>
-      </c>
-      <c r="D47" t="n">
-        <v>3137143</v>
-      </c>
-      <c r="E47" t="n">
-        <v>70.48</v>
-      </c>
-      <c r="F47" t="n">
-        <v>652347.4137931034</v>
-      </c>
-      <c r="G47" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="H47" t="n">
-        <v>40.93</v>
-      </c>
-      <c r="I47" t="n">
-        <v>28.85</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA","EMUDHRA")</f>
-        <v/>
-      </c>
-      <c r="B48" t="n">
-        <v>455.75</v>
-      </c>
-      <c r="C48" t="n">
-        <v>6243996</v>
-      </c>
-      <c r="D48" t="n">
-        <v>585299</v>
-      </c>
-      <c r="E48" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="F48" t="n">
-        <v>54294.44827586207</v>
-      </c>
-      <c r="G48" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="H48" t="n">
-        <v>284.57</v>
-      </c>
-      <c r="I48" t="n">
-        <v>26.68</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICRA","ICRA")</f>
-        <v/>
-      </c>
-      <c r="B49" t="n">
-        <v>5298</v>
-      </c>
-      <c r="C49" t="n">
-        <v>64345</v>
-      </c>
-      <c r="D49" t="n">
-        <v>47118</v>
-      </c>
-      <c r="E49" t="n">
-        <v>73.23</v>
-      </c>
-      <c r="F49" t="n">
-        <v>8746.758620689656</v>
-      </c>
-      <c r="G49" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="H49" t="n">
-        <v>34.09</v>
-      </c>
-      <c r="I49" t="n">
-        <v>24.96</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ELLEN","ELLEN")</f>
-        <v/>
-      </c>
-      <c r="B50" t="n">
-        <v>294.25</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1669388</v>
-      </c>
-      <c r="D50" t="n">
-        <v>839424</v>
-      </c>
-      <c r="E50" t="n">
-        <v>50.28</v>
-      </c>
-      <c r="F50" t="n">
-        <v>181662.5517241379</v>
-      </c>
-      <c r="G50" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="H50" t="n">
-        <v>49.12</v>
-      </c>
-      <c r="I50" t="n">
-        <v>24.7</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INA","INA")</f>
-        <v/>
-      </c>
-      <c r="B51" t="n">
-        <v>124.93</v>
-      </c>
-      <c r="C51" t="n">
-        <v>22232334</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1790719</v>
-      </c>
-      <c r="E51" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="F51" t="n">
-        <v>384970.6206896552</v>
-      </c>
-      <c r="G51" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="H51" t="n">
-        <v>277.75</v>
-      </c>
-      <c r="I51" t="n">
-        <v>22.37</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KODYTECH","KODYTECH")</f>
-        <v/>
-      </c>
-      <c r="B52" t="n">
-        <v>1216.75</v>
-      </c>
-      <c r="C52" t="n">
-        <v>221500</v>
-      </c>
-      <c r="D52" t="n">
-        <v>179200</v>
-      </c>
-      <c r="E52" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="F52" t="n">
-        <v>19962.06896551724</v>
-      </c>
-      <c r="G52" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="H52" t="n">
-        <v>26.95</v>
-      </c>
-      <c r="I52" t="n">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOLARA","SOLARA")</f>
-        <v/>
-      </c>
-      <c r="B53" t="n">
-        <v>568.9</v>
-      </c>
-      <c r="C53" t="n">
-        <v>838612</v>
-      </c>
-      <c r="D53" t="n">
-        <v>363229</v>
-      </c>
-      <c r="E53" t="n">
-        <v>43.31</v>
-      </c>
-      <c r="F53" t="n">
-        <v>101553.0344827586</v>
-      </c>
-      <c r="G53" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="H53" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="I53" t="n">
-        <v>20.66</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/nse/delivery/daily_output/delivery_breakout_20260710.xlsx
+++ b/data/nse/delivery/daily_output/delivery_breakout_20260710.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -504,10 +504,10 @@
         <v>17.23</v>
       </c>
       <c r="F2" t="n">
-        <v>1920031</v>
+        <v>1884860</v>
       </c>
       <c r="G2" t="n">
-        <v>10.37</v>
+        <v>10.56</v>
       </c>
       <c r="H2" t="n">
         <v>5498.93</v>
@@ -534,10 +534,10 @@
         <v>42.07</v>
       </c>
       <c r="F3" t="n">
-        <v>502596</v>
+        <v>487087.5</v>
       </c>
       <c r="G3" t="n">
-        <v>7.68</v>
+        <v>7.93</v>
       </c>
       <c r="H3" t="n">
         <v>1314.33</v>
@@ -564,10 +564,10 @@
         <v>53.8</v>
       </c>
       <c r="F4" t="n">
-        <v>655147</v>
+        <v>628319</v>
       </c>
       <c r="G4" t="n">
-        <v>6.66</v>
+        <v>6.94</v>
       </c>
       <c r="H4" t="n">
         <v>1008.7</v>
@@ -594,10 +594,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1517756</v>
+        <v>1671760</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>5.63</v>
       </c>
       <c r="H5" t="n">
         <v>724</v>
@@ -624,10 +624,10 @@
         <v>91.78</v>
       </c>
       <c r="F6" t="n">
-        <v>6753</v>
+        <v>6822.5</v>
       </c>
       <c r="G6" t="n">
-        <v>108.43</v>
+        <v>107.33</v>
       </c>
       <c r="H6" t="n">
         <v>197.66</v>
@@ -654,10 +654,10 @@
         <v>6.06</v>
       </c>
       <c r="F7" t="n">
-        <v>305011</v>
+        <v>311097.5</v>
       </c>
       <c r="G7" t="n">
-        <v>9.35</v>
+        <v>9.17</v>
       </c>
       <c r="H7" t="n">
         <v>2390.33</v>
@@ -684,10 +684,10 @@
         <v>8.07</v>
       </c>
       <c r="F8" t="n">
-        <v>212961</v>
+        <v>210644.5</v>
       </c>
       <c r="G8" t="n">
-        <v>11.34</v>
+        <v>11.47</v>
       </c>
       <c r="H8" t="n">
         <v>1548.96</v>
@@ -698,901 +698,871 @@
     </row>
     <row r="9">
       <c r="A9">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MRPL","MRPL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IONEXCHANG","IONEXCHANG")</f>
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>162.49</v>
+        <v>468.3</v>
       </c>
       <c r="C9" t="n">
-        <v>37336927</v>
+        <v>12898024</v>
       </c>
       <c r="D9" t="n">
-        <v>6820376</v>
+        <v>1649686</v>
       </c>
       <c r="E9" t="n">
-        <v>18.27</v>
+        <v>12.79</v>
       </c>
       <c r="F9" t="n">
-        <v>1324216</v>
+        <v>204430</v>
       </c>
       <c r="G9" t="n">
-        <v>5.15</v>
+        <v>8.07</v>
       </c>
       <c r="H9" t="n">
-        <v>606.6900000000001</v>
+        <v>604.01</v>
       </c>
       <c r="I9" t="n">
-        <v>110.82</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IONEXCHANG","IONEXCHANG")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RHIM","RHIM")</f>
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>468.3</v>
+        <v>420.35</v>
       </c>
       <c r="C10" t="n">
-        <v>12898024</v>
+        <v>5014433</v>
       </c>
       <c r="D10" t="n">
-        <v>1649686</v>
+        <v>1669819</v>
       </c>
       <c r="E10" t="n">
-        <v>12.79</v>
+        <v>33.3</v>
       </c>
       <c r="F10" t="n">
-        <v>199503</v>
+        <v>142221</v>
       </c>
       <c r="G10" t="n">
-        <v>8.27</v>
+        <v>11.74</v>
       </c>
       <c r="H10" t="n">
-        <v>604.01</v>
+        <v>210.78</v>
       </c>
       <c r="I10" t="n">
-        <v>77.25</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RHIM","RHIM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GOLDIAM","GOLDIAM")</f>
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>420.35</v>
+        <v>378</v>
       </c>
       <c r="C11" t="n">
-        <v>5014433</v>
+        <v>9982384</v>
       </c>
       <c r="D11" t="n">
-        <v>1669819</v>
+        <v>1791399</v>
       </c>
       <c r="E11" t="n">
-        <v>33.3</v>
+        <v>17.95</v>
       </c>
       <c r="F11" t="n">
-        <v>143864</v>
+        <v>332925.5</v>
       </c>
       <c r="G11" t="n">
-        <v>11.61</v>
+        <v>5.38</v>
       </c>
       <c r="H11" t="n">
-        <v>210.78</v>
+        <v>377.33</v>
       </c>
       <c r="I11" t="n">
-        <v>70.19</v>
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GOLDIAM","GOLDIAM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABDL","ABDL")</f>
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>378</v>
+        <v>648.75</v>
       </c>
       <c r="C12" t="n">
-        <v>9982384</v>
+        <v>1420666</v>
       </c>
       <c r="D12" t="n">
-        <v>1791399</v>
+        <v>929614</v>
       </c>
       <c r="E12" t="n">
-        <v>17.95</v>
+        <v>65.44</v>
       </c>
       <c r="F12" t="n">
-        <v>337267</v>
+        <v>150752.5</v>
       </c>
       <c r="G12" t="n">
-        <v>5.31</v>
+        <v>6.17</v>
       </c>
       <c r="H12" t="n">
-        <v>377.33</v>
+        <v>92.17</v>
       </c>
       <c r="I12" t="n">
-        <v>67.70999999999999</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABDL","ABDL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TBOTEK","TBOTEK")</f>
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>648.75</v>
+        <v>1504.9</v>
       </c>
       <c r="C13" t="n">
-        <v>1420666</v>
+        <v>442591</v>
       </c>
       <c r="D13" t="n">
-        <v>929614</v>
+        <v>390174</v>
       </c>
       <c r="E13" t="n">
-        <v>65.44</v>
+        <v>88.16</v>
       </c>
       <c r="F13" t="n">
-        <v>148904</v>
+        <v>54959.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6.24</v>
+        <v>7.1</v>
       </c>
       <c r="H13" t="n">
-        <v>92.17</v>
+        <v>66.61</v>
       </c>
       <c r="I13" t="n">
-        <v>60.31</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TBOTEK","TBOTEK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GODREJIND","GODREJIND")</f>
         <v/>
       </c>
       <c r="B14" t="n">
-        <v>1504.9</v>
+        <v>1417.7</v>
       </c>
       <c r="C14" t="n">
-        <v>442591</v>
+        <v>2661745</v>
       </c>
       <c r="D14" t="n">
-        <v>390174</v>
+        <v>384488</v>
       </c>
       <c r="E14" t="n">
-        <v>88.16</v>
+        <v>14.44</v>
       </c>
       <c r="F14" t="n">
-        <v>53117</v>
+        <v>56469.5</v>
       </c>
       <c r="G14" t="n">
-        <v>7.35</v>
+        <v>6.81</v>
       </c>
       <c r="H14" t="n">
-        <v>66.61</v>
+        <v>377.36</v>
       </c>
       <c r="I14" t="n">
-        <v>58.72</v>
+        <v>54.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GODREJIND","GODREJIND")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:STALLION","STALLION")</f>
         <v/>
       </c>
       <c r="B15" t="n">
-        <v>1417.7</v>
+        <v>204.88</v>
       </c>
       <c r="C15" t="n">
-        <v>2661745</v>
+        <v>16334635</v>
       </c>
       <c r="D15" t="n">
-        <v>384488</v>
+        <v>2619014</v>
       </c>
       <c r="E15" t="n">
-        <v>14.44</v>
+        <v>16.03</v>
       </c>
       <c r="F15" t="n">
-        <v>54457</v>
+        <v>509255.5</v>
       </c>
       <c r="G15" t="n">
-        <v>7.06</v>
+        <v>5.14</v>
       </c>
       <c r="H15" t="n">
-        <v>377.36</v>
+        <v>334.66</v>
       </c>
       <c r="I15" t="n">
-        <v>54.51</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:STALLION","STALLION")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HAPPSTMNDS","HAPPSTMNDS")</f>
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>204.88</v>
+        <v>386.3</v>
       </c>
       <c r="C16" t="n">
-        <v>16334635</v>
+        <v>4373075</v>
       </c>
       <c r="D16" t="n">
-        <v>2619014</v>
+        <v>1218932</v>
       </c>
       <c r="E16" t="n">
-        <v>16.03</v>
+        <v>27.87</v>
       </c>
       <c r="F16" t="n">
-        <v>491381</v>
+        <v>220977</v>
       </c>
       <c r="G16" t="n">
-        <v>5.33</v>
+        <v>5.52</v>
       </c>
       <c r="H16" t="n">
-        <v>334.66</v>
+        <v>168.93</v>
       </c>
       <c r="I16" t="n">
-        <v>53.66</v>
+        <v>47.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HAPPSTMNDS","HAPPSTMNDS")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUMICHEM","SUMICHEM")</f>
         <v/>
       </c>
       <c r="B17" t="n">
-        <v>386.3</v>
+        <v>513.7</v>
       </c>
       <c r="C17" t="n">
-        <v>4373075</v>
+        <v>2258450</v>
       </c>
       <c r="D17" t="n">
-        <v>1218932</v>
+        <v>905164</v>
       </c>
       <c r="E17" t="n">
-        <v>27.87</v>
+        <v>40.08</v>
       </c>
       <c r="F17" t="n">
-        <v>224421</v>
+        <v>132508.5</v>
       </c>
       <c r="G17" t="n">
-        <v>5.43</v>
+        <v>6.83</v>
       </c>
       <c r="H17" t="n">
-        <v>168.93</v>
+        <v>116.02</v>
       </c>
       <c r="I17" t="n">
-        <v>47.09</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUMICHEM","SUMICHEM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZFCVINDIA","ZFCVINDIA")</f>
         <v/>
       </c>
       <c r="B18" t="n">
-        <v>513.7</v>
+        <v>2333.8</v>
       </c>
       <c r="C18" t="n">
-        <v>2258450</v>
+        <v>246194</v>
       </c>
       <c r="D18" t="n">
-        <v>905164</v>
+        <v>192668</v>
       </c>
       <c r="E18" t="n">
-        <v>40.08</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>124584</v>
+        <v>21174.5</v>
       </c>
       <c r="G18" t="n">
-        <v>7.27</v>
+        <v>9.1</v>
       </c>
       <c r="H18" t="n">
-        <v>116.02</v>
+        <v>57.46</v>
       </c>
       <c r="I18" t="n">
-        <v>46.5</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZFCVINDIA","ZFCVINDIA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","MAHLIFE")</f>
         <v/>
       </c>
       <c r="B19" t="n">
-        <v>2333.8</v>
+        <v>378.9</v>
       </c>
       <c r="C19" t="n">
-        <v>246194</v>
+        <v>1292886</v>
       </c>
       <c r="D19" t="n">
-        <v>192668</v>
+        <v>1184617</v>
       </c>
       <c r="E19" t="n">
-        <v>78.26000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="F19" t="n">
-        <v>20838</v>
+        <v>61803</v>
       </c>
       <c r="G19" t="n">
-        <v>9.25</v>
+        <v>19.17</v>
       </c>
       <c r="H19" t="n">
-        <v>57.46</v>
+        <v>48.99</v>
       </c>
       <c r="I19" t="n">
-        <v>44.96</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","MAHLIFE")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMSLIMITED","EMSLIMITED")</f>
         <v/>
       </c>
       <c r="B20" t="n">
-        <v>378.9</v>
+        <v>458.15</v>
       </c>
       <c r="C20" t="n">
-        <v>1292886</v>
+        <v>2680107</v>
       </c>
       <c r="D20" t="n">
-        <v>1184617</v>
+        <v>899272</v>
       </c>
       <c r="E20" t="n">
-        <v>91.63</v>
+        <v>33.55</v>
       </c>
       <c r="F20" t="n">
-        <v>61803</v>
+        <v>164676.5</v>
       </c>
       <c r="G20" t="n">
-        <v>19.17</v>
+        <v>5.46</v>
       </c>
       <c r="H20" t="n">
-        <v>48.99</v>
+        <v>122.79</v>
       </c>
       <c r="I20" t="n">
-        <v>44.89</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMSLIMITED","EMSLIMITED")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOBIKWIK","MOBIKWIK")</f>
         <v/>
       </c>
       <c r="B21" t="n">
-        <v>458.15</v>
+        <v>221.45</v>
       </c>
       <c r="C21" t="n">
-        <v>2680107</v>
+        <v>9125473</v>
       </c>
       <c r="D21" t="n">
-        <v>899272</v>
+        <v>1846860</v>
       </c>
       <c r="E21" t="n">
-        <v>33.55</v>
+        <v>20.24</v>
       </c>
       <c r="F21" t="n">
-        <v>170521</v>
+        <v>245023</v>
       </c>
       <c r="G21" t="n">
-        <v>5.27</v>
+        <v>7.54</v>
       </c>
       <c r="H21" t="n">
-        <v>122.79</v>
+        <v>202.08</v>
       </c>
       <c r="I21" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOBIKWIK","MOBIKWIK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SENCO","SENCO")</f>
         <v/>
       </c>
       <c r="B22" t="n">
-        <v>221.45</v>
+        <v>362.15</v>
       </c>
       <c r="C22" t="n">
-        <v>9125473</v>
+        <v>4077698</v>
       </c>
       <c r="D22" t="n">
-        <v>1846860</v>
+        <v>1103581</v>
       </c>
       <c r="E22" t="n">
-        <v>20.24</v>
+        <v>27.06</v>
       </c>
       <c r="F22" t="n">
-        <v>243565</v>
+        <v>188797</v>
       </c>
       <c r="G22" t="n">
-        <v>7.58</v>
+        <v>5.85</v>
       </c>
       <c r="H22" t="n">
-        <v>202.08</v>
+        <v>147.67</v>
       </c>
       <c r="I22" t="n">
-        <v>40.9</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SENCO","SENCO")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTMF","MUTHOOTMF")</f>
         <v/>
       </c>
       <c r="B23" t="n">
-        <v>362.15</v>
+        <v>235.26</v>
       </c>
       <c r="C23" t="n">
-        <v>4077698</v>
+        <v>19681749</v>
       </c>
       <c r="D23" t="n">
-        <v>1103581</v>
+        <v>1613616</v>
       </c>
       <c r="E23" t="n">
-        <v>27.06</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>193516</v>
+        <v>140253</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>11.51</v>
       </c>
       <c r="H23" t="n">
-        <v>147.67</v>
+        <v>463.03</v>
       </c>
       <c r="I23" t="n">
-        <v>39.97</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTMF","MUTHOOTMF")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IFBIND","IFBIND")</f>
         <v/>
       </c>
       <c r="B24" t="n">
-        <v>235.26</v>
+        <v>1380.5</v>
       </c>
       <c r="C24" t="n">
-        <v>19681749</v>
+        <v>658386</v>
       </c>
       <c r="D24" t="n">
-        <v>1613616</v>
+        <v>259855</v>
       </c>
       <c r="E24" t="n">
-        <v>8.199999999999999</v>
+        <v>39.47</v>
       </c>
       <c r="F24" t="n">
-        <v>144018</v>
+        <v>26604</v>
       </c>
       <c r="G24" t="n">
-        <v>11.2</v>
+        <v>9.77</v>
       </c>
       <c r="H24" t="n">
-        <v>463.03</v>
+        <v>90.89</v>
       </c>
       <c r="I24" t="n">
-        <v>37.96</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IFBIND","IFBIND")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAXESTATES","MAXESTATES")</f>
         <v/>
       </c>
       <c r="B25" t="n">
-        <v>1380.5</v>
+        <v>449.5</v>
       </c>
       <c r="C25" t="n">
-        <v>658386</v>
+        <v>877910</v>
       </c>
       <c r="D25" t="n">
-        <v>259855</v>
+        <v>790461</v>
       </c>
       <c r="E25" t="n">
-        <v>39.47</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>27246</v>
+        <v>24606.5</v>
       </c>
       <c r="G25" t="n">
-        <v>9.539999999999999</v>
+        <v>32.12</v>
       </c>
       <c r="H25" t="n">
-        <v>90.89</v>
+        <v>39.46</v>
       </c>
       <c r="I25" t="n">
-        <v>35.87</v>
+        <v>35.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAXESTATES","MAXESTATES")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PGHL","PGHL")</f>
         <v/>
       </c>
       <c r="B26" t="n">
-        <v>449.5</v>
+        <v>6839</v>
       </c>
       <c r="C26" t="n">
-        <v>877910</v>
+        <v>82938</v>
       </c>
       <c r="D26" t="n">
-        <v>790461</v>
+        <v>51538</v>
       </c>
       <c r="E26" t="n">
-        <v>90.04000000000001</v>
+        <v>62.14</v>
       </c>
       <c r="F26" t="n">
-        <v>24796</v>
+        <v>7523</v>
       </c>
       <c r="G26" t="n">
-        <v>31.88</v>
+        <v>6.85</v>
       </c>
       <c r="H26" t="n">
-        <v>39.46</v>
+        <v>56.72</v>
       </c>
       <c r="I26" t="n">
-        <v>35.53</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PGHL","PGHL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SKFINDUS","SKFINDUS")</f>
         <v/>
       </c>
       <c r="B27" t="n">
-        <v>6839</v>
+        <v>2830.4</v>
       </c>
       <c r="C27" t="n">
-        <v>82938</v>
+        <v>146009</v>
       </c>
       <c r="D27" t="n">
-        <v>51538</v>
+        <v>120539</v>
       </c>
       <c r="E27" t="n">
-        <v>62.14</v>
+        <v>82.56</v>
       </c>
       <c r="F27" t="n">
-        <v>7808</v>
+        <v>18134</v>
       </c>
       <c r="G27" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="H27" t="n">
-        <v>56.72</v>
+        <v>41.33</v>
       </c>
       <c r="I27" t="n">
-        <v>35.25</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SKFINDUS","SKFINDUS")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANHLIFE","CANHLIFE")</f>
         <v/>
       </c>
       <c r="B28" t="n">
-        <v>2830.4</v>
+        <v>144.03</v>
       </c>
       <c r="C28" t="n">
-        <v>146009</v>
+        <v>2458962</v>
       </c>
       <c r="D28" t="n">
-        <v>120539</v>
+        <v>2184455</v>
       </c>
       <c r="E28" t="n">
-        <v>82.56</v>
+        <v>88.84</v>
       </c>
       <c r="F28" t="n">
-        <v>17864</v>
+        <v>300124</v>
       </c>
       <c r="G28" t="n">
-        <v>6.75</v>
+        <v>7.28</v>
       </c>
       <c r="H28" t="n">
-        <v>41.33</v>
+        <v>35.42</v>
       </c>
       <c r="I28" t="n">
-        <v>34.12</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANHLIFE","CANHLIFE")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BECTORFOOD","BECTORFOOD")</f>
         <v/>
       </c>
       <c r="B29" t="n">
-        <v>144.03</v>
+        <v>169.37</v>
       </c>
       <c r="C29" t="n">
-        <v>2458962</v>
+        <v>2452161</v>
       </c>
       <c r="D29" t="n">
-        <v>2184455</v>
+        <v>1739659</v>
       </c>
       <c r="E29" t="n">
-        <v>88.84</v>
+        <v>70.94</v>
       </c>
       <c r="F29" t="n">
-        <v>300124</v>
+        <v>318416.5</v>
       </c>
       <c r="G29" t="n">
-        <v>7.28</v>
+        <v>5.46</v>
       </c>
       <c r="H29" t="n">
-        <v>35.42</v>
+        <v>41.53</v>
       </c>
       <c r="I29" t="n">
-        <v>31.46</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BECTORFOOD","BECTORFOOD")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCPSUBK","HDFCPSUBK")</f>
         <v/>
       </c>
       <c r="B30" t="n">
-        <v>169.37</v>
+        <v>85.41</v>
       </c>
       <c r="C30" t="n">
-        <v>2452161</v>
+        <v>4186849</v>
       </c>
       <c r="D30" t="n">
-        <v>1739659</v>
+        <v>3433510</v>
       </c>
       <c r="E30" t="n">
-        <v>70.94</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>310585</v>
+        <v>46932</v>
       </c>
       <c r="G30" t="n">
-        <v>5.6</v>
+        <v>73.16</v>
       </c>
       <c r="H30" t="n">
-        <v>41.53</v>
+        <v>35.76</v>
       </c>
       <c r="I30" t="n">
-        <v>29.46</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCPSUBK","HDFCPSUBK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBFC","SBFC")</f>
         <v/>
       </c>
       <c r="B31" t="n">
-        <v>85.41</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>4186849</v>
+        <v>4451123</v>
       </c>
       <c r="D31" t="n">
-        <v>3433510</v>
+        <v>3137143</v>
       </c>
       <c r="E31" t="n">
-        <v>82.01000000000001</v>
+        <v>70.48</v>
       </c>
       <c r="F31" t="n">
-        <v>45800</v>
+        <v>457320.5</v>
       </c>
       <c r="G31" t="n">
-        <v>74.97</v>
+        <v>6.86</v>
       </c>
       <c r="H31" t="n">
-        <v>35.76</v>
+        <v>40.93</v>
       </c>
       <c r="I31" t="n">
-        <v>29.33</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBFC","SBFC")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA","EMUDHRA")</f>
         <v/>
       </c>
       <c r="B32" t="n">
-        <v>91.95999999999999</v>
+        <v>455.75</v>
       </c>
       <c r="C32" t="n">
-        <v>4451123</v>
+        <v>6243996</v>
       </c>
       <c r="D32" t="n">
-        <v>3137143</v>
+        <v>585299</v>
       </c>
       <c r="E32" t="n">
-        <v>70.48</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>455078</v>
+        <v>31961</v>
       </c>
       <c r="G32" t="n">
-        <v>6.89</v>
+        <v>18.31</v>
       </c>
       <c r="H32" t="n">
-        <v>40.93</v>
+        <v>284.57</v>
       </c>
       <c r="I32" t="n">
-        <v>28.85</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA","EMUDHRA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICRA","ICRA")</f>
         <v/>
       </c>
       <c r="B33" t="n">
-        <v>455.75</v>
+        <v>5298</v>
       </c>
       <c r="C33" t="n">
-        <v>6243996</v>
+        <v>64345</v>
       </c>
       <c r="D33" t="n">
-        <v>585299</v>
+        <v>47118</v>
       </c>
       <c r="E33" t="n">
-        <v>9.369999999999999</v>
+        <v>73.23</v>
       </c>
       <c r="F33" t="n">
-        <v>31913</v>
+        <v>5885</v>
       </c>
       <c r="G33" t="n">
-        <v>18.34</v>
+        <v>8.01</v>
       </c>
       <c r="H33" t="n">
-        <v>284.57</v>
+        <v>34.09</v>
       </c>
       <c r="I33" t="n">
-        <v>26.68</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICRA","ICRA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ELLEN","ELLEN")</f>
         <v/>
       </c>
       <c r="B34" t="n">
-        <v>5298</v>
+        <v>294.25</v>
       </c>
       <c r="C34" t="n">
-        <v>64345</v>
+        <v>1669388</v>
       </c>
       <c r="D34" t="n">
-        <v>47118</v>
+        <v>839424</v>
       </c>
       <c r="E34" t="n">
-        <v>73.23</v>
+        <v>50.28</v>
       </c>
       <c r="F34" t="n">
-        <v>5249</v>
+        <v>118629</v>
       </c>
       <c r="G34" t="n">
-        <v>8.98</v>
+        <v>7.08</v>
       </c>
       <c r="H34" t="n">
-        <v>34.09</v>
+        <v>49.12</v>
       </c>
       <c r="I34" t="n">
-        <v>24.96</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ELLEN","ELLEN")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INA","INA")</f>
         <v/>
       </c>
       <c r="B35" t="n">
-        <v>294.25</v>
+        <v>124.93</v>
       </c>
       <c r="C35" t="n">
-        <v>1669388</v>
+        <v>22232334</v>
       </c>
       <c r="D35" t="n">
-        <v>839424</v>
+        <v>1790719</v>
       </c>
       <c r="E35" t="n">
-        <v>50.28</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>122144</v>
+        <v>264100</v>
       </c>
       <c r="G35" t="n">
-        <v>6.87</v>
+        <v>6.78</v>
       </c>
       <c r="H35" t="n">
-        <v>49.12</v>
+        <v>277.75</v>
       </c>
       <c r="I35" t="n">
-        <v>24.7</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INA","INA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KODYTECH","KODYTECH")</f>
         <v/>
       </c>
       <c r="B36" t="n">
-        <v>124.93</v>
+        <v>1216.75</v>
       </c>
       <c r="C36" t="n">
-        <v>22232334</v>
+        <v>221500</v>
       </c>
       <c r="D36" t="n">
-        <v>1790719</v>
+        <v>179200</v>
       </c>
       <c r="E36" t="n">
-        <v>8.050000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>264131</v>
+        <v>9550</v>
       </c>
       <c r="G36" t="n">
-        <v>6.78</v>
+        <v>18.76</v>
       </c>
       <c r="H36" t="n">
-        <v>277.75</v>
+        <v>26.95</v>
       </c>
       <c r="I36" t="n">
-        <v>22.37</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KODYTECH","KODYTECH")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ITDC","ITDC")</f>
         <v/>
       </c>
       <c r="B37" t="n">
-        <v>1216.75</v>
+        <v>716.8</v>
       </c>
       <c r="C37" t="n">
-        <v>221500</v>
+        <v>3469655</v>
       </c>
       <c r="D37" t="n">
-        <v>179200</v>
+        <v>293035</v>
       </c>
       <c r="E37" t="n">
-        <v>80.90000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>9500</v>
+        <v>51823</v>
       </c>
       <c r="G37" t="n">
-        <v>18.86</v>
+        <v>5.65</v>
       </c>
       <c r="H37" t="n">
-        <v>26.95</v>
+        <v>248.7</v>
       </c>
       <c r="I37" t="n">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ITDC","ITDC")</f>
-        <v/>
-      </c>
-      <c r="B38" t="n">
-        <v>716.8</v>
-      </c>
-      <c r="C38" t="n">
-        <v>3469655</v>
-      </c>
-      <c r="D38" t="n">
-        <v>293035</v>
-      </c>
-      <c r="E38" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="F38" t="n">
-        <v>50591</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="H38" t="n">
-        <v>248.7</v>
-      </c>
-      <c r="I38" t="n">
         <v>21</v>
       </c>
     </row>

--- a/data/nse/delivery/daily_output/delivery_breakout_20260710.xlsx
+++ b/data/nse/delivery/daily_output/delivery_breakout_20260710.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -433,7 +433,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -504,10 +504,10 @@
         <v>17.23</v>
       </c>
       <c r="F2" t="n">
-        <v>1884860</v>
+        <v>3119380.785714286</v>
       </c>
       <c r="G2" t="n">
-        <v>10.56</v>
+        <v>6.38</v>
       </c>
       <c r="H2" t="n">
         <v>5498.93</v>
@@ -518,1052 +518,1502 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CDSL","CDSL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIXON","DIXON")</f>
         <v/>
       </c>
       <c r="B3" t="n">
-        <v>1431.9</v>
+        <v>13421</v>
       </c>
       <c r="C3" t="n">
-        <v>9178914</v>
+        <v>1689462</v>
       </c>
       <c r="D3" t="n">
-        <v>3861959</v>
+        <v>591632</v>
       </c>
       <c r="E3" t="n">
-        <v>42.07</v>
+        <v>35.02</v>
       </c>
       <c r="F3" t="n">
-        <v>487087.5</v>
+        <v>177086.4285714286</v>
       </c>
       <c r="G3" t="n">
-        <v>7.93</v>
+        <v>3.34</v>
       </c>
       <c r="H3" t="n">
-        <v>1314.33</v>
+        <v>2267.43</v>
       </c>
       <c r="I3" t="n">
-        <v>552.99</v>
+        <v>794.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","DRREDDY")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CDSL","CDSL")</f>
         <v/>
       </c>
       <c r="B4" t="n">
-        <v>1244.3</v>
+        <v>1431.9</v>
       </c>
       <c r="C4" t="n">
-        <v>8106606</v>
+        <v>9178914</v>
       </c>
       <c r="D4" t="n">
-        <v>4361177</v>
+        <v>3861959</v>
       </c>
       <c r="E4" t="n">
-        <v>53.8</v>
+        <v>42.07</v>
       </c>
       <c r="F4" t="n">
-        <v>628319</v>
+        <v>659137.9285714285</v>
       </c>
       <c r="G4" t="n">
-        <v>6.94</v>
+        <v>5.86</v>
       </c>
       <c r="H4" t="n">
-        <v>1008.7</v>
+        <v>1314.33</v>
       </c>
       <c r="I4" t="n">
-        <v>542.66</v>
+        <v>552.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY","DELHIVERY")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","DRREDDY")</f>
         <v/>
       </c>
       <c r="B5" t="n">
-        <v>520.3</v>
+        <v>1244.3</v>
       </c>
       <c r="C5" t="n">
-        <v>13914959</v>
+        <v>8106606</v>
       </c>
       <c r="D5" t="n">
-        <v>9405977</v>
+        <v>4361177</v>
       </c>
       <c r="E5" t="n">
-        <v>67.59999999999999</v>
+        <v>53.8</v>
       </c>
       <c r="F5" t="n">
-        <v>1671760</v>
+        <v>870913.75</v>
       </c>
       <c r="G5" t="n">
-        <v>5.63</v>
+        <v>5.01</v>
       </c>
       <c r="H5" t="n">
-        <v>724</v>
+        <v>1008.7</v>
       </c>
       <c r="I5" t="n">
-        <v>489.39</v>
+        <v>542.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ETHOSLTD","ETHOSLTD")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DELHIVERY","DELHIVERY")</f>
         <v/>
       </c>
       <c r="B6" t="n">
-        <v>2477.5</v>
+        <v>520.3</v>
       </c>
       <c r="C6" t="n">
-        <v>797816</v>
+        <v>13914959</v>
       </c>
       <c r="D6" t="n">
-        <v>732248</v>
+        <v>9405977</v>
       </c>
       <c r="E6" t="n">
-        <v>91.78</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>6822.5</v>
+        <v>2604788.392857143</v>
       </c>
       <c r="G6" t="n">
-        <v>107.33</v>
+        <v>3.61</v>
       </c>
       <c r="H6" t="n">
-        <v>197.66</v>
+        <v>724</v>
       </c>
       <c r="I6" t="n">
-        <v>181.41</v>
+        <v>489.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZENSARTECH","ZENSARTECH")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ETHOSLTD","ETHOSLTD")</f>
         <v/>
       </c>
       <c r="B7" t="n">
-        <v>508.25</v>
+        <v>2477.5</v>
       </c>
       <c r="C7" t="n">
-        <v>47030557</v>
+        <v>797816</v>
       </c>
       <c r="D7" t="n">
-        <v>2851264</v>
+        <v>732248</v>
       </c>
       <c r="E7" t="n">
-        <v>6.06</v>
+        <v>91.78</v>
       </c>
       <c r="F7" t="n">
-        <v>311097.5</v>
+        <v>9100.964285714286</v>
       </c>
       <c r="G7" t="n">
-        <v>9.17</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>2390.33</v>
+        <v>197.66</v>
       </c>
       <c r="I7" t="n">
-        <v>144.92</v>
+        <v>181.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NEWGEN","NEWGEN")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZENSARTECH","ZENSARTECH")</f>
         <v/>
       </c>
       <c r="B8" t="n">
-        <v>517.2</v>
+        <v>508.25</v>
       </c>
       <c r="C8" t="n">
-        <v>29948995</v>
+        <v>47030557</v>
       </c>
       <c r="D8" t="n">
-        <v>2415435</v>
+        <v>2851264</v>
       </c>
       <c r="E8" t="n">
-        <v>8.07</v>
+        <v>6.06</v>
       </c>
       <c r="F8" t="n">
-        <v>210644.5</v>
+        <v>563413.5357142857</v>
       </c>
       <c r="G8" t="n">
-        <v>11.47</v>
+        <v>5.06</v>
       </c>
       <c r="H8" t="n">
-        <v>1548.96</v>
+        <v>2390.33</v>
       </c>
       <c r="I8" t="n">
-        <v>124.93</v>
+        <v>144.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IONEXCHANG","IONEXCHANG")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:J&amp;KBANK","J&amp;KBANK")</f>
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>468.3</v>
+        <v>192.65</v>
       </c>
       <c r="C9" t="n">
-        <v>12898024</v>
+        <v>22820672</v>
       </c>
       <c r="D9" t="n">
-        <v>1649686</v>
+        <v>7449900</v>
       </c>
       <c r="E9" t="n">
-        <v>12.79</v>
+        <v>32.65</v>
       </c>
       <c r="F9" t="n">
-        <v>204430</v>
+        <v>1958599.357142857</v>
       </c>
       <c r="G9" t="n">
-        <v>8.07</v>
+        <v>3.8</v>
       </c>
       <c r="H9" t="n">
-        <v>604.01</v>
+        <v>439.64</v>
       </c>
       <c r="I9" t="n">
-        <v>77.25</v>
+        <v>143.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RHIM","RHIM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UJJIVANSFB","UJJIVANSFB")</f>
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>420.35</v>
+        <v>65.27</v>
       </c>
       <c r="C10" t="n">
-        <v>5014433</v>
+        <v>39570140</v>
       </c>
       <c r="D10" t="n">
-        <v>1669819</v>
+        <v>20855448</v>
       </c>
       <c r="E10" t="n">
-        <v>33.3</v>
+        <v>52.71</v>
       </c>
       <c r="F10" t="n">
-        <v>142221</v>
+        <v>6956272.928571428</v>
       </c>
       <c r="G10" t="n">
-        <v>11.74</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>210.78</v>
+        <v>258.27</v>
       </c>
       <c r="I10" t="n">
-        <v>70.19</v>
+        <v>136.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GOLDIAM","GOLDIAM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INOXWIND","INOXWIND")</f>
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>378</v>
+        <v>82.61</v>
       </c>
       <c r="C11" t="n">
-        <v>9982384</v>
+        <v>32213482</v>
       </c>
       <c r="D11" t="n">
-        <v>1791399</v>
+        <v>16164772</v>
       </c>
       <c r="E11" t="n">
-        <v>17.95</v>
+        <v>50.18</v>
       </c>
       <c r="F11" t="n">
-        <v>332925.5</v>
+        <v>4093695.214285714</v>
       </c>
       <c r="G11" t="n">
-        <v>5.38</v>
+        <v>3.95</v>
       </c>
       <c r="H11" t="n">
-        <v>377.33</v>
+        <v>266.12</v>
       </c>
       <c r="I11" t="n">
-        <v>67.70999999999999</v>
+        <v>133.54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABDL","ABDL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NEWGEN","NEWGEN")</f>
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>648.75</v>
+        <v>517.2</v>
       </c>
       <c r="C12" t="n">
-        <v>1420666</v>
+        <v>29948995</v>
       </c>
       <c r="D12" t="n">
-        <v>929614</v>
+        <v>2415435</v>
       </c>
       <c r="E12" t="n">
-        <v>65.44</v>
+        <v>8.07</v>
       </c>
       <c r="F12" t="n">
-        <v>150752.5</v>
+        <v>389331.9285714286</v>
       </c>
       <c r="G12" t="n">
-        <v>6.17</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>92.17</v>
+        <v>1548.96</v>
       </c>
       <c r="I12" t="n">
-        <v>60.31</v>
+        <v>124.93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TBOTEK","TBOTEK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MRPL","MRPL")</f>
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>1504.9</v>
+        <v>162.49</v>
       </c>
       <c r="C13" t="n">
-        <v>442591</v>
+        <v>37336927</v>
       </c>
       <c r="D13" t="n">
-        <v>390174</v>
+        <v>6820376</v>
       </c>
       <c r="E13" t="n">
-        <v>88.16</v>
+        <v>18.27</v>
       </c>
       <c r="F13" t="n">
-        <v>54959.5</v>
+        <v>1831409.321428571</v>
       </c>
       <c r="G13" t="n">
-        <v>7.1</v>
+        <v>3.72</v>
       </c>
       <c r="H13" t="n">
-        <v>66.61</v>
+        <v>606.6900000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>58.72</v>
+        <v>110.82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GODREJIND","GODREJIND")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GREAVESCOT","GREAVESCOT")</f>
         <v/>
       </c>
       <c r="B14" t="n">
-        <v>1417.7</v>
+        <v>263.6</v>
       </c>
       <c r="C14" t="n">
-        <v>2661745</v>
+        <v>20117335</v>
       </c>
       <c r="D14" t="n">
-        <v>384488</v>
+        <v>3405606</v>
       </c>
       <c r="E14" t="n">
-        <v>14.44</v>
+        <v>16.93</v>
       </c>
       <c r="F14" t="n">
-        <v>56469.5</v>
+        <v>998346.6785714285</v>
       </c>
       <c r="G14" t="n">
-        <v>6.81</v>
+        <v>3.41</v>
       </c>
       <c r="H14" t="n">
-        <v>377.36</v>
+        <v>530.29</v>
       </c>
       <c r="I14" t="n">
-        <v>54.51</v>
+        <v>89.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:STALLION","STALLION")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IONEXCHANG","IONEXCHANG")</f>
         <v/>
       </c>
       <c r="B15" t="n">
-        <v>204.88</v>
+        <v>468.3</v>
       </c>
       <c r="C15" t="n">
-        <v>16334635</v>
+        <v>12898024</v>
       </c>
       <c r="D15" t="n">
-        <v>2619014</v>
+        <v>1649686</v>
       </c>
       <c r="E15" t="n">
-        <v>16.03</v>
+        <v>12.79</v>
       </c>
       <c r="F15" t="n">
-        <v>509255.5</v>
+        <v>282024.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5.14</v>
+        <v>5.85</v>
       </c>
       <c r="H15" t="n">
-        <v>334.66</v>
+        <v>604.01</v>
       </c>
       <c r="I15" t="n">
-        <v>53.66</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HAPPSTMNDS","HAPPSTMNDS")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ARE&amp;M","ARE&amp;M")</f>
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>386.3</v>
+        <v>890.05</v>
       </c>
       <c r="C16" t="n">
-        <v>4373075</v>
+        <v>1615861</v>
       </c>
       <c r="D16" t="n">
-        <v>1218932</v>
+        <v>859855</v>
       </c>
       <c r="E16" t="n">
-        <v>27.87</v>
+        <v>53.21</v>
       </c>
       <c r="F16" t="n">
-        <v>220977</v>
+        <v>224281.8928571429</v>
       </c>
       <c r="G16" t="n">
-        <v>5.52</v>
+        <v>3.83</v>
       </c>
       <c r="H16" t="n">
-        <v>168.93</v>
+        <v>143.82</v>
       </c>
       <c r="I16" t="n">
-        <v>47.09</v>
+        <v>76.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUMICHEM","SUMICHEM")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RHIM","RHIM")</f>
         <v/>
       </c>
       <c r="B17" t="n">
-        <v>513.7</v>
+        <v>420.35</v>
       </c>
       <c r="C17" t="n">
-        <v>2258450</v>
+        <v>5014433</v>
       </c>
       <c r="D17" t="n">
-        <v>905164</v>
+        <v>1669819</v>
       </c>
       <c r="E17" t="n">
-        <v>40.08</v>
+        <v>33.3</v>
       </c>
       <c r="F17" t="n">
-        <v>132508.5</v>
+        <v>394092.4642857143</v>
       </c>
       <c r="G17" t="n">
-        <v>6.83</v>
+        <v>4.24</v>
       </c>
       <c r="H17" t="n">
-        <v>116.02</v>
+        <v>210.78</v>
       </c>
       <c r="I17" t="n">
-        <v>46.5</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZFCVINDIA","ZFCVINDIA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GOLDIAM","GOLDIAM")</f>
         <v/>
       </c>
       <c r="B18" t="n">
-        <v>2333.8</v>
+        <v>378</v>
       </c>
       <c r="C18" t="n">
-        <v>246194</v>
+        <v>9982384</v>
       </c>
       <c r="D18" t="n">
-        <v>192668</v>
+        <v>1791399</v>
       </c>
       <c r="E18" t="n">
-        <v>78.26000000000001</v>
+        <v>17.95</v>
       </c>
       <c r="F18" t="n">
-        <v>21174.5</v>
+        <v>391561.9285714286</v>
       </c>
       <c r="G18" t="n">
-        <v>9.1</v>
+        <v>4.58</v>
       </c>
       <c r="H18" t="n">
-        <v>57.46</v>
+        <v>377.33</v>
       </c>
       <c r="I18" t="n">
-        <v>44.96</v>
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","MAHLIFE")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUEJET","BLUEJET")</f>
         <v/>
       </c>
       <c r="B19" t="n">
-        <v>378.9</v>
+        <v>624.05</v>
       </c>
       <c r="C19" t="n">
-        <v>1292886</v>
+        <v>4844866</v>
       </c>
       <c r="D19" t="n">
-        <v>1184617</v>
+        <v>1062858</v>
       </c>
       <c r="E19" t="n">
-        <v>91.63</v>
+        <v>21.94</v>
       </c>
       <c r="F19" t="n">
-        <v>61803</v>
+        <v>288283.0714285714</v>
       </c>
       <c r="G19" t="n">
-        <v>19.17</v>
+        <v>3.69</v>
       </c>
       <c r="H19" t="n">
-        <v>48.99</v>
+        <v>302.34</v>
       </c>
       <c r="I19" t="n">
-        <v>44.89</v>
+        <v>66.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMSLIMITED","EMSLIMITED")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EIEL","EIEL")</f>
         <v/>
       </c>
       <c r="B20" t="n">
-        <v>458.15</v>
+        <v>244.49</v>
       </c>
       <c r="C20" t="n">
-        <v>2680107</v>
+        <v>9010315</v>
       </c>
       <c r="D20" t="n">
-        <v>899272</v>
+        <v>2710990</v>
       </c>
       <c r="E20" t="n">
-        <v>33.55</v>
+        <v>30.09</v>
       </c>
       <c r="F20" t="n">
-        <v>164676.5</v>
+        <v>813423.7857142857</v>
       </c>
       <c r="G20" t="n">
-        <v>5.46</v>
+        <v>3.33</v>
       </c>
       <c r="H20" t="n">
-        <v>122.79</v>
+        <v>220.29</v>
       </c>
       <c r="I20" t="n">
-        <v>41.2</v>
+        <v>66.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOBIKWIK","MOBIKWIK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","BRIGADE")</f>
         <v/>
       </c>
       <c r="B21" t="n">
-        <v>221.45</v>
+        <v>574.6</v>
       </c>
       <c r="C21" t="n">
-        <v>9125473</v>
+        <v>2703568</v>
       </c>
       <c r="D21" t="n">
-        <v>1846860</v>
+        <v>1139441</v>
       </c>
       <c r="E21" t="n">
-        <v>20.24</v>
+        <v>42.15</v>
       </c>
       <c r="F21" t="n">
-        <v>245023</v>
+        <v>364054.0357142857</v>
       </c>
       <c r="G21" t="n">
-        <v>7.54</v>
+        <v>3.13</v>
       </c>
       <c r="H21" t="n">
-        <v>202.08</v>
+        <v>155.35</v>
       </c>
       <c r="I21" t="n">
-        <v>40.9</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SENCO","SENCO")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABDL","ABDL")</f>
         <v/>
       </c>
       <c r="B22" t="n">
-        <v>362.15</v>
+        <v>648.75</v>
       </c>
       <c r="C22" t="n">
-        <v>4077698</v>
+        <v>1420666</v>
       </c>
       <c r="D22" t="n">
-        <v>1103581</v>
+        <v>929614</v>
       </c>
       <c r="E22" t="n">
-        <v>27.06</v>
+        <v>65.44</v>
       </c>
       <c r="F22" t="n">
-        <v>188797</v>
+        <v>198799.5357142857</v>
       </c>
       <c r="G22" t="n">
-        <v>5.85</v>
+        <v>4.68</v>
       </c>
       <c r="H22" t="n">
-        <v>147.67</v>
+        <v>92.17</v>
       </c>
       <c r="I22" t="n">
-        <v>39.97</v>
+        <v>60.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTMF","MUTHOOTMF")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEG","HEG")</f>
         <v/>
       </c>
       <c r="B23" t="n">
-        <v>235.26</v>
+        <v>545.05</v>
       </c>
       <c r="C23" t="n">
-        <v>19681749</v>
+        <v>5160132</v>
       </c>
       <c r="D23" t="n">
-        <v>1613616</v>
+        <v>1091995</v>
       </c>
       <c r="E23" t="n">
-        <v>8.199999999999999</v>
+        <v>21.16</v>
       </c>
       <c r="F23" t="n">
-        <v>140253</v>
+        <v>346614.6428571428</v>
       </c>
       <c r="G23" t="n">
-        <v>11.51</v>
+        <v>3.15</v>
       </c>
       <c r="H23" t="n">
-        <v>463.03</v>
+        <v>281.25</v>
       </c>
       <c r="I23" t="n">
-        <v>37.96</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IFBIND","IFBIND")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TBOTEK","TBOTEK")</f>
         <v/>
       </c>
       <c r="B24" t="n">
-        <v>1380.5</v>
+        <v>1504.9</v>
       </c>
       <c r="C24" t="n">
-        <v>658386</v>
+        <v>442591</v>
       </c>
       <c r="D24" t="n">
-        <v>259855</v>
+        <v>390174</v>
       </c>
       <c r="E24" t="n">
-        <v>39.47</v>
+        <v>88.16</v>
       </c>
       <c r="F24" t="n">
-        <v>26604</v>
+        <v>122557.3214285714</v>
       </c>
       <c r="G24" t="n">
-        <v>9.77</v>
+        <v>3.18</v>
       </c>
       <c r="H24" t="n">
-        <v>90.89</v>
+        <v>66.61</v>
       </c>
       <c r="I24" t="n">
-        <v>35.87</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAXESTATES","MAXESTATES")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GODREJIND","GODREJIND")</f>
         <v/>
       </c>
       <c r="B25" t="n">
-        <v>449.5</v>
+        <v>1417.7</v>
       </c>
       <c r="C25" t="n">
-        <v>877910</v>
+        <v>2661745</v>
       </c>
       <c r="D25" t="n">
-        <v>790461</v>
+        <v>384488</v>
       </c>
       <c r="E25" t="n">
-        <v>90.04000000000001</v>
+        <v>14.44</v>
       </c>
       <c r="F25" t="n">
-        <v>24606.5</v>
+        <v>58096.85714285714</v>
       </c>
       <c r="G25" t="n">
-        <v>32.12</v>
+        <v>6.62</v>
       </c>
       <c r="H25" t="n">
-        <v>39.46</v>
+        <v>377.36</v>
       </c>
       <c r="I25" t="n">
-        <v>35.53</v>
+        <v>54.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PGHL","PGHL")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:STALLION","STALLION")</f>
         <v/>
       </c>
       <c r="B26" t="n">
-        <v>6839</v>
+        <v>204.88</v>
       </c>
       <c r="C26" t="n">
-        <v>82938</v>
+        <v>16334635</v>
       </c>
       <c r="D26" t="n">
-        <v>51538</v>
+        <v>2619014</v>
       </c>
       <c r="E26" t="n">
-        <v>62.14</v>
+        <v>16.03</v>
       </c>
       <c r="F26" t="n">
-        <v>7523</v>
+        <v>627382.0357142857</v>
       </c>
       <c r="G26" t="n">
-        <v>6.85</v>
+        <v>4.17</v>
       </c>
       <c r="H26" t="n">
-        <v>56.72</v>
+        <v>334.66</v>
       </c>
       <c r="I26" t="n">
-        <v>35.25</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SKFINDUS","SKFINDUS")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HAPPSTMNDS","HAPPSTMNDS")</f>
         <v/>
       </c>
       <c r="B27" t="n">
-        <v>2830.4</v>
+        <v>386.3</v>
       </c>
       <c r="C27" t="n">
-        <v>146009</v>
+        <v>4373075</v>
       </c>
       <c r="D27" t="n">
-        <v>120539</v>
+        <v>1218932</v>
       </c>
       <c r="E27" t="n">
-        <v>82.56</v>
+        <v>27.87</v>
       </c>
       <c r="F27" t="n">
-        <v>18134</v>
+        <v>337398.6785714286</v>
       </c>
       <c r="G27" t="n">
-        <v>6.65</v>
+        <v>3.61</v>
       </c>
       <c r="H27" t="n">
-        <v>41.33</v>
+        <v>168.93</v>
       </c>
       <c r="I27" t="n">
-        <v>34.12</v>
+        <v>47.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANHLIFE","CANHLIFE")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZFCVINDIA","ZFCVINDIA")</f>
         <v/>
       </c>
       <c r="B28" t="n">
-        <v>144.03</v>
+        <v>2333.8</v>
       </c>
       <c r="C28" t="n">
-        <v>2458962</v>
+        <v>246194</v>
       </c>
       <c r="D28" t="n">
-        <v>2184455</v>
+        <v>192668</v>
       </c>
       <c r="E28" t="n">
-        <v>88.84</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>300124</v>
+        <v>60311.85714285714</v>
       </c>
       <c r="G28" t="n">
-        <v>7.28</v>
+        <v>3.19</v>
       </c>
       <c r="H28" t="n">
-        <v>35.42</v>
+        <v>57.46</v>
       </c>
       <c r="I28" t="n">
-        <v>31.46</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BECTORFOOD","BECTORFOOD")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","MAHLIFE")</f>
         <v/>
       </c>
       <c r="B29" t="n">
-        <v>169.37</v>
+        <v>378.9</v>
       </c>
       <c r="C29" t="n">
-        <v>2452161</v>
+        <v>1292886</v>
       </c>
       <c r="D29" t="n">
-        <v>1739659</v>
+        <v>1184617</v>
       </c>
       <c r="E29" t="n">
-        <v>70.94</v>
+        <v>91.63</v>
       </c>
       <c r="F29" t="n">
-        <v>318416.5</v>
+        <v>75557.71428571429</v>
       </c>
       <c r="G29" t="n">
-        <v>5.46</v>
+        <v>15.68</v>
       </c>
       <c r="H29" t="n">
-        <v>41.53</v>
+        <v>48.99</v>
       </c>
       <c r="I29" t="n">
-        <v>29.46</v>
+        <v>44.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCPSUBK","HDFCPSUBK")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMSLIMITED","EMSLIMITED")</f>
         <v/>
       </c>
       <c r="B30" t="n">
-        <v>85.41</v>
+        <v>458.15</v>
       </c>
       <c r="C30" t="n">
-        <v>4186849</v>
+        <v>2680107</v>
       </c>
       <c r="D30" t="n">
-        <v>3433510</v>
+        <v>899272</v>
       </c>
       <c r="E30" t="n">
-        <v>82.01000000000001</v>
+        <v>33.55</v>
       </c>
       <c r="F30" t="n">
-        <v>46932</v>
+        <v>243233.0714285714</v>
       </c>
       <c r="G30" t="n">
-        <v>73.16</v>
+        <v>3.7</v>
       </c>
       <c r="H30" t="n">
-        <v>35.76</v>
+        <v>122.79</v>
       </c>
       <c r="I30" t="n">
-        <v>29.33</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBFC","SBFC")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOBIKWIK","MOBIKWIK")</f>
         <v/>
       </c>
       <c r="B31" t="n">
-        <v>91.95999999999999</v>
+        <v>221.45</v>
       </c>
       <c r="C31" t="n">
-        <v>4451123</v>
+        <v>9125473</v>
       </c>
       <c r="D31" t="n">
-        <v>3137143</v>
+        <v>1846860</v>
       </c>
       <c r="E31" t="n">
-        <v>70.48</v>
+        <v>20.24</v>
       </c>
       <c r="F31" t="n">
-        <v>457320.5</v>
+        <v>356602.1785714286</v>
       </c>
       <c r="G31" t="n">
-        <v>6.86</v>
+        <v>5.18</v>
       </c>
       <c r="H31" t="n">
-        <v>40.93</v>
+        <v>202.08</v>
       </c>
       <c r="I31" t="n">
-        <v>28.85</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA","EMUDHRA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NORTHARC","NORTHARC")</f>
         <v/>
       </c>
       <c r="B32" t="n">
-        <v>455.75</v>
+        <v>325.3</v>
       </c>
       <c r="C32" t="n">
-        <v>6243996</v>
+        <v>2149647</v>
       </c>
       <c r="D32" t="n">
-        <v>585299</v>
+        <v>1251298</v>
       </c>
       <c r="E32" t="n">
-        <v>9.369999999999999</v>
+        <v>58.21</v>
       </c>
       <c r="F32" t="n">
-        <v>31961</v>
+        <v>314014.0714285714</v>
       </c>
       <c r="G32" t="n">
-        <v>18.31</v>
+        <v>3.98</v>
       </c>
       <c r="H32" t="n">
-        <v>284.57</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>26.68</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICRA","ICRA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SENCO","SENCO")</f>
         <v/>
       </c>
       <c r="B33" t="n">
-        <v>5298</v>
+        <v>362.15</v>
       </c>
       <c r="C33" t="n">
-        <v>64345</v>
+        <v>4077698</v>
       </c>
       <c r="D33" t="n">
-        <v>47118</v>
+        <v>1103581</v>
       </c>
       <c r="E33" t="n">
-        <v>73.23</v>
+        <v>27.06</v>
       </c>
       <c r="F33" t="n">
-        <v>5885</v>
+        <v>322556.75</v>
       </c>
       <c r="G33" t="n">
-        <v>8.01</v>
+        <v>3.42</v>
       </c>
       <c r="H33" t="n">
-        <v>34.09</v>
+        <v>147.67</v>
       </c>
       <c r="I33" t="n">
-        <v>24.96</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ELLEN","ELLEN")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MUTHOOTMF","MUTHOOTMF")</f>
         <v/>
       </c>
       <c r="B34" t="n">
-        <v>294.25</v>
+        <v>235.26</v>
       </c>
       <c r="C34" t="n">
-        <v>1669388</v>
+        <v>19681749</v>
       </c>
       <c r="D34" t="n">
-        <v>839424</v>
+        <v>1613616</v>
       </c>
       <c r="E34" t="n">
-        <v>50.28</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>118629</v>
+        <v>184639.25</v>
       </c>
       <c r="G34" t="n">
-        <v>7.08</v>
+        <v>8.74</v>
       </c>
       <c r="H34" t="n">
-        <v>49.12</v>
+        <v>463.03</v>
       </c>
       <c r="I34" t="n">
-        <v>24.7</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INA","INA")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IFBIND","IFBIND")</f>
         <v/>
       </c>
       <c r="B35" t="n">
-        <v>124.93</v>
+        <v>1380.5</v>
       </c>
       <c r="C35" t="n">
-        <v>22232334</v>
+        <v>658386</v>
       </c>
       <c r="D35" t="n">
-        <v>1790719</v>
+        <v>259855</v>
       </c>
       <c r="E35" t="n">
-        <v>8.050000000000001</v>
+        <v>39.47</v>
       </c>
       <c r="F35" t="n">
-        <v>264100</v>
+        <v>35873.17857142857</v>
       </c>
       <c r="G35" t="n">
-        <v>6.78</v>
+        <v>7.24</v>
       </c>
       <c r="H35" t="n">
-        <v>277.75</v>
+        <v>90.89</v>
       </c>
       <c r="I35" t="n">
-        <v>22.37</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KODYTECH","KODYTECH")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAXESTATES","MAXESTATES")</f>
         <v/>
       </c>
       <c r="B36" t="n">
-        <v>1216.75</v>
+        <v>449.5</v>
       </c>
       <c r="C36" t="n">
-        <v>221500</v>
+        <v>877910</v>
       </c>
       <c r="D36" t="n">
-        <v>179200</v>
+        <v>790461</v>
       </c>
       <c r="E36" t="n">
-        <v>80.90000000000001</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>9550</v>
+        <v>38293.10714285714</v>
       </c>
       <c r="G36" t="n">
-        <v>18.76</v>
+        <v>20.64</v>
       </c>
       <c r="H36" t="n">
-        <v>26.95</v>
+        <v>39.46</v>
       </c>
       <c r="I36" t="n">
-        <v>21.8</v>
+        <v>35.53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ITDC","ITDC")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PGHL","PGHL")</f>
         <v/>
       </c>
       <c r="B37" t="n">
-        <v>716.8</v>
+        <v>6839</v>
       </c>
       <c r="C37" t="n">
-        <v>3469655</v>
+        <v>82938</v>
       </c>
       <c r="D37" t="n">
-        <v>293035</v>
+        <v>51538</v>
       </c>
       <c r="E37" t="n">
-        <v>8.449999999999999</v>
+        <v>62.14</v>
       </c>
       <c r="F37" t="n">
-        <v>51823</v>
+        <v>10245.39285714286</v>
       </c>
       <c r="G37" t="n">
-        <v>5.65</v>
+        <v>5.03</v>
       </c>
       <c r="H37" t="n">
-        <v>248.7</v>
+        <v>56.72</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>35.25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UTIAMC","UTIAMC")</f>
+        <v/>
+      </c>
+      <c r="B38" t="n">
+        <v>1004.3</v>
+      </c>
+      <c r="C38" t="n">
+        <v>663822</v>
+      </c>
+      <c r="D38" t="n">
+        <v>346882</v>
+      </c>
+      <c r="E38" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="F38" t="n">
+        <v>97900.14285714286</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="H38" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="I38" t="n">
+        <v>34.84</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUDARSCHEM","SUDARSCHEM")</f>
+        <v/>
+      </c>
+      <c r="B39" t="n">
+        <v>999.25</v>
+      </c>
+      <c r="C39" t="n">
+        <v>615230</v>
+      </c>
+      <c r="D39" t="n">
+        <v>343807</v>
+      </c>
+      <c r="E39" t="n">
+        <v>55.88</v>
+      </c>
+      <c r="F39" t="n">
+        <v>102693.5357142857</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H39" t="n">
+        <v>61.48</v>
+      </c>
+      <c r="I39" t="n">
+        <v>34.35</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SKFINDUS","SKFINDUS")</f>
+        <v/>
+      </c>
+      <c r="B40" t="n">
+        <v>2830.4</v>
+      </c>
+      <c r="C40" t="n">
+        <v>146009</v>
+      </c>
+      <c r="D40" t="n">
+        <v>120539</v>
+      </c>
+      <c r="E40" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="F40" t="n">
+        <v>30848.25</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="H40" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="I40" t="n">
+        <v>34.12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CANHLIFE","CANHLIFE")</f>
+        <v/>
+      </c>
+      <c r="B41" t="n">
+        <v>144.03</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2458962</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2184455</v>
+      </c>
+      <c r="E41" t="n">
+        <v>88.84</v>
+      </c>
+      <c r="F41" t="n">
+        <v>362476.75</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H41" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="I41" t="n">
+        <v>31.46</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AYE","AYE")</f>
+        <v/>
+      </c>
+      <c r="B42" t="n">
+        <v>168.82</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2422421</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1857984</v>
+      </c>
+      <c r="E42" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="F42" t="n">
+        <v>484992.1785714286</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H42" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>31.37</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BECTORFOOD","BECTORFOOD")</f>
+        <v/>
+      </c>
+      <c r="B43" t="n">
+        <v>169.37</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2452161</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1739659</v>
+      </c>
+      <c r="E43" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="F43" t="n">
+        <v>442473.1428571428</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H43" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="I43" t="n">
+        <v>29.46</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATUL","ATUL")</f>
+        <v/>
+      </c>
+      <c r="B44" t="n">
+        <v>6236</v>
+      </c>
+      <c r="C44" t="n">
+        <v>69678</v>
+      </c>
+      <c r="D44" t="n">
+        <v>47167</v>
+      </c>
+      <c r="E44" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="F44" t="n">
+        <v>11998.25</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H44" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="I44" t="n">
+        <v>29.41</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HDFCPSUBK","HDFCPSUBK")</f>
+        <v/>
+      </c>
+      <c r="B45" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4186849</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3433510</v>
+      </c>
+      <c r="E45" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="F45" t="n">
+        <v>411764.8928571428</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="H45" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="I45" t="n">
+        <v>29.33</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SBFC","SBFC")</f>
+        <v/>
+      </c>
+      <c r="B46" t="n">
+        <v>91.95999999999999</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4451123</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3137143</v>
+      </c>
+      <c r="E46" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="F46" t="n">
+        <v>664324.0357142857</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H46" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="I46" t="n">
+        <v>28.85</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EMUDHRA","EMUDHRA")</f>
+        <v/>
+      </c>
+      <c r="B47" t="n">
+        <v>455.75</v>
+      </c>
+      <c r="C47" t="n">
+        <v>6243996</v>
+      </c>
+      <c r="D47" t="n">
+        <v>585299</v>
+      </c>
+      <c r="E47" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>55409.03571428572</v>
+      </c>
+      <c r="G47" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="H47" t="n">
+        <v>284.57</v>
+      </c>
+      <c r="I47" t="n">
+        <v>26.68</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICRA","ICRA")</f>
+        <v/>
+      </c>
+      <c r="B48" t="n">
+        <v>5298</v>
+      </c>
+      <c r="C48" t="n">
+        <v>64345</v>
+      </c>
+      <c r="D48" t="n">
+        <v>47118</v>
+      </c>
+      <c r="E48" t="n">
+        <v>73.23</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8989.214285714286</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="H48" t="n">
+        <v>34.09</v>
+      </c>
+      <c r="I48" t="n">
+        <v>24.96</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ELLEN","ELLEN")</f>
+        <v/>
+      </c>
+      <c r="B49" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1669388</v>
+      </c>
+      <c r="D49" t="n">
+        <v>839424</v>
+      </c>
+      <c r="E49" t="n">
+        <v>50.28</v>
+      </c>
+      <c r="F49" t="n">
+        <v>178502.7857142857</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H49" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="I49" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INA","INA")</f>
+        <v/>
+      </c>
+      <c r="B50" t="n">
+        <v>124.93</v>
+      </c>
+      <c r="C50" t="n">
+        <v>22232334</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1790719</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="F50" t="n">
+        <v>377839.7142857143</v>
+      </c>
+      <c r="G50" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H50" t="n">
+        <v>277.75</v>
+      </c>
+      <c r="I50" t="n">
+        <v>22.37</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KODYTECH","KODYTECH")</f>
+        <v/>
+      </c>
+      <c r="B51" t="n">
+        <v>1216.75</v>
+      </c>
+      <c r="C51" t="n">
+        <v>221500</v>
+      </c>
+      <c r="D51" t="n">
+        <v>179200</v>
+      </c>
+      <c r="E51" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>20585.71428571429</v>
+      </c>
+      <c r="G51" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="I51" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SOLARA","SOLARA")</f>
+        <v/>
+      </c>
+      <c r="B52" t="n">
+        <v>568.9</v>
+      </c>
+      <c r="C52" t="n">
+        <v>838612</v>
+      </c>
+      <c r="D52" t="n">
+        <v>363229</v>
+      </c>
+      <c r="E52" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="F52" t="n">
+        <v>101443.3214285714</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H52" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="I52" t="n">
+        <v>20.66</v>
       </c>
     </row>
   </sheetData>
